--- a/株式会社鶴岡中央青果/案件マスター_鶴岡中央青果_260923.xlsx
+++ b/株式会社鶴岡中央青果/案件マスター_鶴岡中央青果_260923.xlsx
@@ -13,20 +13,27 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS (貸方)" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SGA" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PL" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM→" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社概要" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLハイライト" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BSハイライト" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="取引先" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="仕入先" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="株主" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="取締役" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="従業員" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="拠点(本社等)" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="不動産(所有)" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設備" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月別売上" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="その他" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VR→" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="修正PL" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="修正BS" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ネットキャッシュ" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年買法" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EV EBITDAマルチプル" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="株式価値" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM→" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会社概要" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLハイライト" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BSハイライト" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="取引先" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="仕入先" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="株主" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="取締役" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="従業員" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="拠点(本社等)" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="不動産(所有)" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設備" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月別売上" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="その他" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35,10 +42,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0,;[Red]△#,##0,;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red]△0.0%;&quot;-&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0;[Red]△#,##0;&quot;-&quot;"/>
+    <numFmt numFmtId="166" formatCode="0&quot;倍&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0;[Red]△#,##0;&quot;-&quot;"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -132,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -164,24 +172,27 @@
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -629,6 +640,1588 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ネットキャッシュ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>評価基準日：2026年3月31日（修正後BS）。単位：千円（入力は円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>金額</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>判断根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>現金及び預金</t>
+        </is>
+      </c>
+      <c r="C5" s="7">
+        <f>修正BS!E5</f>
+        <v>210887077</v>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>全額をキャッシュライクとする（運転資金は考慮しない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>投資有価証券（フィデアHD株式・時価）</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>8442000</v>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>事業運営に供されていない上場株式。(株)庄果株式・信金出資は取引関係上の保有のため除外</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>キャッシュライク 計</t>
+        </is>
+      </c>
+      <c r="C7" s="9">
+        <f>C5+C6</f>
+        <v>219329077</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>長期借入金</t>
+        </is>
+      </c>
+      <c r="C8" s="7">
+        <f>修正BS!E37</f>
+        <v>361058000</v>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>有利子負債</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>未払法人税等</t>
+        </is>
+      </c>
+      <c r="C9" s="7">
+        <f>修正BS!E35</f>
+        <v>1851300</v>
+      </c>
+      <c r="D9" s="18" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>デットライク 計</t>
+        </is>
+      </c>
+      <c r="C10" s="9">
+        <f>C8+C9</f>
+        <v>362909300</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>ネットキャッシュ</t>
+        </is>
+      </c>
+      <c r="C11" s="11">
+        <f>C7-C10</f>
+        <v>-143580223</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>※預り保証金8,980千円・保証金33,303千円は事業上の預託・預り金としてネットキャッシュに含めていない（取扱いは要確認）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>年買法（コストアプローチ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>想定株式価値＝時価純資産＋営業権（基準営業利益×倍率）。単位：千円（入力は円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>時価純資産</t>
+        </is>
+      </c>
+      <c r="C4" s="17">
+        <f>修正BS!E43</f>
+        <v>55318457.4285715</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>基準営業利益（税考慮後・加重平均）</t>
+        </is>
+      </c>
+      <c r="C5" s="17">
+        <f>修正PL!E21</f>
+        <v>696266.620500001</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="4" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>営業権倍率</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>1倍</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>2倍</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>3倍</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>倍率</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>時価純資産</t>
+        </is>
+      </c>
+      <c r="C9" s="7">
+        <f>$C$4</f>
+        <v>55318457.4285715</v>
+      </c>
+      <c r="D9" s="7">
+        <f>$C$4</f>
+        <v>55318457.4285715</v>
+      </c>
+      <c r="E9" s="7">
+        <f>$C$4</f>
+        <v>55318457.4285715</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>営業権</t>
+        </is>
+      </c>
+      <c r="C10" s="7">
+        <f>MAX($C$5,0)*C8</f>
+        <v>696266.620500001</v>
+      </c>
+      <c r="D10" s="7">
+        <f>MAX($C$5,0)*D8</f>
+        <v>1392533.241</v>
+      </c>
+      <c r="E10" s="7">
+        <f>MAX($C$5,0)*E8</f>
+        <v>2088799.8615</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>想定株式価値</t>
+        </is>
+      </c>
+      <c r="C11" s="11">
+        <f>C9+C10</f>
+        <v>56014724.0490715</v>
+      </c>
+      <c r="D11" s="11">
+        <f>D9+D10</f>
+        <v>56710990.6695715</v>
+      </c>
+      <c r="E11" s="11">
+        <f>E9+E10</f>
+        <v>57407257.2900715</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>※営業権倍率1〜3倍は国内中小企業M&amp;Aのボリュームゾーン。基準営業利益がマイナスの場合は営業権ゼロ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>（参考）賞与正常化を行わない場合の基準営業利益</t>
+        </is>
+      </c>
+      <c r="C15" s="17">
+        <f>C5-修正PL!E10*(1-0.34)*0.5</f>
+        <v>2915326.458</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>（参考）想定株式価値</t>
+        </is>
+      </c>
+      <c r="C16" s="7">
+        <f>$C$4+MAX($C$15,0)*C8</f>
+        <v>58233783.8865715</v>
+      </c>
+      <c r="D16" s="7">
+        <f>$C$4+MAX($C$15,0)*D8</f>
+        <v>61149110.3445715</v>
+      </c>
+      <c r="E16" s="7">
+        <f>$C$4+MAX($C$15,0)*E8</f>
+        <v>64064436.8025715</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EV/EBITDAマルチプル法（マーケットアプローチ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>想定株式価値＝基準EBITDA×倍率×(1−非流動性ディスカウント)＋ネットキャッシュ。単位：千円（入力は円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>基準EBITDA（加重平均）</t>
+        </is>
+      </c>
+      <c r="C4" s="17">
+        <f>修正PL!E22</f>
+        <v>11994440.425</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>ネットキャッシュ</t>
+        </is>
+      </c>
+      <c r="C5" s="17">
+        <f>ネットキャッシュ!C11</f>
+        <v>-143580223</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>非流動性ディスカウント</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="4" t="inlineStr"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>マルチプル倍率</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>3倍</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>4倍</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>5倍</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>倍率</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>EV（EBITDA×倍率）</t>
+        </is>
+      </c>
+      <c r="C10" s="7">
+        <f>$C$4*C9</f>
+        <v>35983321.275</v>
+      </c>
+      <c r="D10" s="7">
+        <f>$C$4*D9</f>
+        <v>47977761.7</v>
+      </c>
+      <c r="E10" s="7">
+        <f>$C$4*E9</f>
+        <v>59972202.125</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>非流動性ディスカウント</t>
+        </is>
+      </c>
+      <c r="C11" s="7">
+        <f>-C10*$C$6</f>
+        <v>-10794996.3825</v>
+      </c>
+      <c r="D11" s="7">
+        <f>-D10*$C$6</f>
+        <v>-14393328.51</v>
+      </c>
+      <c r="E11" s="7">
+        <f>-E10*$C$6</f>
+        <v>-17991660.6375</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>ネットキャッシュ</t>
+        </is>
+      </c>
+      <c r="C12" s="7">
+        <f>$C$5</f>
+        <v>-143580223</v>
+      </c>
+      <c r="D12" s="7">
+        <f>$C$5</f>
+        <v>-143580223</v>
+      </c>
+      <c r="E12" s="7">
+        <f>$C$5</f>
+        <v>-143580223</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>想定株式価値（算定値）</t>
+        </is>
+      </c>
+      <c r="C13" s="11">
+        <f>SUM(C10:C12)</f>
+        <v>-118391898.1075</v>
+      </c>
+      <c r="D13" s="11">
+        <f>SUM(D10:D12)</f>
+        <v>-109995789.81</v>
+      </c>
+      <c r="E13" s="11">
+        <f>SUM(E10:E12)</f>
+        <v>-101599681.5125</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>※倍率3〜5倍は国内中小企業M&amp;Aの実務水準。卸売市場関連の上場会社の倍率は算定日時点の株価で更新が必要（要確認）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>※算定値がマイナスの場合、ネットデット（有利子負債−現預金等）が事業価値を上回ることを示す。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式価値の試算結果（集計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>単位：千円（入力は円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>アプローチ</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>下限</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>上限</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>コストアプローチ（年買法）</t>
+        </is>
+      </c>
+      <c r="C5" s="7">
+        <f>年買法!C11</f>
+        <v>56014724.0490715</v>
+      </c>
+      <c r="D5" s="7">
+        <f>年買法!E11</f>
+        <v>57407257.2900715</v>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>営業権倍率1〜3倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>マーケットアプローチ（EV/EBITDAマルチプル法）</t>
+        </is>
+      </c>
+      <c r="C6" s="7">
+        <f>'EV EBITDAマルチプル'!C13</f>
+        <v>-118391898.1075</v>
+      </c>
+      <c r="D6" s="7">
+        <f>'EV EBITDAマルチプル'!E13</f>
+        <v>-101599681.5125</v>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>EV/EBITDA3〜5倍、非流動性ディスカウント30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>インカムアプローチ（DCF法）</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>不採用（詳細な事業計画が存在せず算定困難）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000B3041"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>会社概要（基本情報ページの原本）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="4" t="inlineStr"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>商号</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>株式会社鶴岡中央青果</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>本店所在地</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>山形県鶴岡市宝田一丁目4番20号</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>設立</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>1973年（昭和48年）11月22日</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>代表者</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>代表取締役　岡部 寛</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>資本金</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>40,000千円</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>発行済株式総数</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>4,000株（発行可能株式総数5,000株、譲渡制限あり：取締役会の承認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>事業内容</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>青果物（野菜・果実）の卸売（鶴岡市宝田における地方卸売市場の開設・運営および卸売業）、包装資材・肥料等の販売、パッケージ（小分け・包装）業務、倉庫業</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>登記上の目的</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>1 青果物の販売及び卸売の業務　2 倉庫業　3 前号に附帯する一切の業務</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>機関設計</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>取締役会設置会社／監査役設置会社（監査の範囲を会計に限定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>従業員数</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>職員名簿24名（うち正社員等17名・嘱託/再雇用/試用3名・パート3名・アルバイト1名）＋常勤役員2名（2026年9月1日現在）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>決算期</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>営業時間／定休日</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>6時〜17時（推察。概況説明書上「開店6時・閉店5時」）／水・日・祝日</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>主要取引金融機関</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>鶴岡信用金庫、山形銀行、荘内銀行、日本政策金融公庫</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>顧問税理士</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>池田昭一税理士事務所（山形県酒田市）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Webサイト</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>https://www.turu-chu.co.jp/（検索結果により存在を確認。法人事業概況説明書では「HPなし」と記載：要確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>直近業績(2026/3期)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>売上高 1,195,893千円／営業利益 5,859千円／経常利益 8,067千円</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>財務ハイライト（P/L）・調整後EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>単位：千円（入力は円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>2024年3月期
+(第51期)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>2025年3月期
+(第52期)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>2026年3月期
+(第53期)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>3期平均</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>直近2期平均</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>売上高</t>
+        </is>
+      </c>
+      <c r="C5" s="17">
+        <f>PL!C10</f>
+        <v>1178489098</v>
+      </c>
+      <c r="D5" s="17">
+        <f>PL!E10</f>
+        <v>1181947340</v>
+      </c>
+      <c r="E5" s="17">
+        <f>PL!G10</f>
+        <v>1195893269</v>
+      </c>
+      <c r="F5" s="17">
+        <f>AVERAGE(C5:E5)</f>
+        <v>1185443235.66667</v>
+      </c>
+      <c r="G5" s="17">
+        <f>AVERAGE(D5:E5)</f>
+        <v>1188920304.5</v>
+      </c>
+      <c r="H5" s="18" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>売上総利益</t>
+        </is>
+      </c>
+      <c r="C6" s="7">
+        <f>PL!C15</f>
+        <v>219580189</v>
+      </c>
+      <c r="D6" s="7">
+        <f>PL!E15</f>
+        <v>211295514</v>
+      </c>
+      <c r="E6" s="7">
+        <f>PL!G15</f>
+        <v>199010966</v>
+      </c>
+      <c r="F6" s="7">
+        <f>AVERAGE(C6:E6)</f>
+        <v>209962223</v>
+      </c>
+      <c r="G6" s="7">
+        <f>AVERAGE(D6:E6)</f>
+        <v>205153240</v>
+      </c>
+      <c r="H6" s="18" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>売上総利益率</t>
+        </is>
+      </c>
+      <c r="C7" s="15">
+        <f>IFERROR(C6/C5,"")</f>
+        <v>0.186323479252075</v>
+      </c>
+      <c r="D7" s="15">
+        <f>IFERROR(D6/D5,"")</f>
+        <v>0.178768974597464</v>
+      </c>
+      <c r="E7" s="15">
+        <f>IFERROR(E6/E5,"")</f>
+        <v>0.166411979362014</v>
+      </c>
+      <c r="H7" s="18" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="C8" s="7">
+        <f>PL!C16</f>
+        <v>214823441</v>
+      </c>
+      <c r="D8" s="7">
+        <f>PL!E16</f>
+        <v>215718454</v>
+      </c>
+      <c r="E8" s="7">
+        <f>PL!G16</f>
+        <v>193151054</v>
+      </c>
+      <c r="F8" s="7">
+        <f>AVERAGE(C8:E8)</f>
+        <v>207897649.666667</v>
+      </c>
+      <c r="G8" s="7">
+        <f>AVERAGE(D8:E8)</f>
+        <v>204434754</v>
+      </c>
+      <c r="H8" s="18" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>営業利益</t>
+        </is>
+      </c>
+      <c r="C9" s="17">
+        <f>PL!C17</f>
+        <v>4756748</v>
+      </c>
+      <c r="D9" s="17">
+        <f>PL!E17</f>
+        <v>-4422940</v>
+      </c>
+      <c r="E9" s="17">
+        <f>PL!G17</f>
+        <v>5859912</v>
+      </c>
+      <c r="F9" s="17">
+        <f>AVERAGE(C9:E9)</f>
+        <v>2064573.33333333</v>
+      </c>
+      <c r="G9" s="17">
+        <f>AVERAGE(D9:E9)</f>
+        <v>718486</v>
+      </c>
+      <c r="H9" s="18" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>減価償却費</t>
+        </is>
+      </c>
+      <c r="C10" s="7">
+        <f>SGA!C31</f>
+        <v>13663684</v>
+      </c>
+      <c r="D10" s="7">
+        <f>SGA!E31</f>
+        <v>12557564</v>
+      </c>
+      <c r="E10" s="7">
+        <f>SGA!G31</f>
+        <v>8878970</v>
+      </c>
+      <c r="F10" s="7">
+        <f>AVERAGE(C10:E10)</f>
+        <v>11700072.6666667</v>
+      </c>
+      <c r="G10" s="7">
+        <f>AVERAGE(D10:E10)</f>
+        <v>10718267</v>
+      </c>
+      <c r="H10" s="18" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>EBITDA（営業利益＋減価償却費）</t>
+        </is>
+      </c>
+      <c r="C11" s="9">
+        <f>C9+C10</f>
+        <v>18420432</v>
+      </c>
+      <c r="D11" s="9">
+        <f>D9+D10</f>
+        <v>8134624</v>
+      </c>
+      <c r="E11" s="9">
+        <f>E9+E10</f>
+        <v>14738882</v>
+      </c>
+      <c r="F11" s="9">
+        <f>AVERAGE(C11:E11)</f>
+        <v>13764646</v>
+      </c>
+      <c r="G11" s="9">
+        <f>AVERAGE(D11:E11)</f>
+        <v>11436753</v>
+      </c>
+      <c r="H11" s="18" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>【調整項目】（修正PLシートを参照）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>①役員報酬の正常化</t>
+        </is>
+      </c>
+      <c r="C13" s="7">
+        <f>修正PL!C9</f>
+        <v>3082000</v>
+      </c>
+      <c r="D13" s="7">
+        <f>修正PL!D9</f>
+        <v>3082000</v>
+      </c>
+      <c r="E13" s="7">
+        <f>修正PL!E9</f>
+        <v>-4094000</v>
+      </c>
+      <c r="F13" s="7">
+        <f>AVERAGE(C13:E13)</f>
+        <v>690000</v>
+      </c>
+      <c r="G13" s="7">
+        <f>AVERAGE(D13:E13)</f>
+        <v>-506000</v>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>代表者・配偶者報酬を新体制の報酬（仮定8,000千円）に置換、社保15%連動</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>②賞与の正常化</t>
+        </is>
+      </c>
+      <c r="C14" s="7">
+        <f>修正PL!C10</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="7">
+        <f>修正PL!D10</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="7">
+        <f>修正PL!E10</f>
+        <v>-6724423.75</v>
+      </c>
+      <c r="F14" s="7">
+        <f>AVERAGE(C14:E14)</f>
+        <v>-2241474.58333333</v>
+      </c>
+      <c r="G14" s="7">
+        <f>AVERAGE(D14:E14)</f>
+        <v>-3362211.875</v>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>2026/3期は賞与計上なし。前2期平均相当を費用計上（仮説）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>③受取奨励金（純額）の加算</t>
+        </is>
+      </c>
+      <c r="C15" s="7">
+        <f>修正PL!C12</f>
+        <v>2178508</v>
+      </c>
+      <c r="D15" s="7">
+        <f>修正PL!D12</f>
+        <v>2314707</v>
+      </c>
+      <c r="E15" s="7">
+        <f>修正PL!E12</f>
+        <v>2418448</v>
+      </c>
+      <c r="F15" s="7">
+        <f>AVERAGE(C15:E15)</f>
+        <v>2303887.66666667</v>
+      </c>
+      <c r="G15" s="7">
+        <f>AVERAGE(D15:E15)</f>
+        <v>2366577.5</v>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>毎期経常的に発生する事業関連収益</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>④寄付金の加算</t>
+        </is>
+      </c>
+      <c r="C16" s="7">
+        <f>修正PL!C11</f>
+        <v>13000</v>
+      </c>
+      <c r="D16" s="7">
+        <f>修正PL!D11</f>
+        <v>71000</v>
+      </c>
+      <c r="E16" s="7">
+        <f>修正PL!E11</f>
+        <v>11000</v>
+      </c>
+      <c r="F16" s="7">
+        <f>AVERAGE(C16:E16)</f>
+        <v>31666.6666666667</v>
+      </c>
+      <c r="G16" s="7">
+        <f>AVERAGE(D16:E16)</f>
+        <v>41000</v>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>譲渡後に発生しない費用</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>調整額 計</t>
+        </is>
+      </c>
+      <c r="C17" s="7">
+        <f>C13+C14+C15+C16</f>
+        <v>5273508</v>
+      </c>
+      <c r="D17" s="7">
+        <f>D13+D14+D15+D16</f>
+        <v>5467707</v>
+      </c>
+      <c r="E17" s="7">
+        <f>E13+E14+E15+E16</f>
+        <v>-8388975.75</v>
+      </c>
+      <c r="F17" s="7">
+        <f>AVERAGE(C17:E17)</f>
+        <v>784079.750000001</v>
+      </c>
+      <c r="G17" s="7">
+        <f>AVERAGE(D17:E17)</f>
+        <v>-1460634.375</v>
+      </c>
+      <c r="H17" s="18" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>調整後EBITDA</t>
+        </is>
+      </c>
+      <c r="C18" s="11">
+        <f>C11+C17</f>
+        <v>23693940</v>
+      </c>
+      <c r="D18" s="11">
+        <f>D11+D17</f>
+        <v>13602331</v>
+      </c>
+      <c r="E18" s="11">
+        <f>E11+E17</f>
+        <v>6349906.25</v>
+      </c>
+      <c r="F18" s="11">
+        <f>AVERAGE(C18:E18)</f>
+        <v>14548725.75</v>
+      </c>
+      <c r="G18" s="11">
+        <f>AVERAGE(D18:E18)</f>
+        <v>9976118.625</v>
+      </c>
+      <c r="H18" s="18" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>経常利益</t>
+        </is>
+      </c>
+      <c r="C20" s="7">
+        <f>PL!C29</f>
+        <v>11316540</v>
+      </c>
+      <c r="D20" s="7">
+        <f>PL!E29</f>
+        <v>2181381</v>
+      </c>
+      <c r="E20" s="7">
+        <f>PL!G29</f>
+        <v>8067784</v>
+      </c>
+      <c r="F20" s="7">
+        <f>AVERAGE(C20:E20)</f>
+        <v>7188568.33333333</v>
+      </c>
+      <c r="G20" s="7">
+        <f>AVERAGE(D20:E20)</f>
+        <v>5124582.5</v>
+      </c>
+      <c r="H20" s="18" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>当期純利益</t>
+        </is>
+      </c>
+      <c r="C21" s="7">
+        <f>PL!C39</f>
+        <v>9106898</v>
+      </c>
+      <c r="D21" s="7">
+        <f>PL!E39</f>
+        <v>2928899</v>
+      </c>
+      <c r="E21" s="7">
+        <f>PL!G39</f>
+        <v>-15084655</v>
+      </c>
+      <c r="F21" s="7">
+        <f>AVERAGE(C21:E21)</f>
+        <v>-1016286</v>
+      </c>
+      <c r="G21" s="7">
+        <f>AVERAGE(D21:E21)</f>
+        <v>-6077878</v>
+      </c>
+      <c r="H21" s="18" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>支払利息</t>
+        </is>
+      </c>
+      <c r="C22" s="7">
+        <f>PL!C25</f>
+        <v>3962441</v>
+      </c>
+      <c r="D22" s="7">
+        <f>PL!E25</f>
+        <v>4040547</v>
+      </c>
+      <c r="E22" s="7">
+        <f>PL!G25</f>
+        <v>3895556</v>
+      </c>
+      <c r="F22" s="7">
+        <f>AVERAGE(C22:E22)</f>
+        <v>3966181.33333333</v>
+      </c>
+      <c r="G22" s="7">
+        <f>AVERAGE(D22:E22)</f>
+        <v>3968051.5</v>
+      </c>
+      <c r="H22" s="18" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>人件費（役員報酬・給与・賞与・法定福利等）</t>
+        </is>
+      </c>
+      <c r="C23" s="7">
+        <f>SGA!C5+SGA!C6+SGA!C7+SGA!C8+SGA!C9+SGA!C10+SGA!C11</f>
+        <v>120274546</v>
+      </c>
+      <c r="D23" s="7">
+        <f>SGA!E5+SGA!E6+SGA!E7+SGA!E8+SGA!E9+SGA!E10+SGA!E11</f>
+        <v>121407097</v>
+      </c>
+      <c r="E23" s="7">
+        <f>SGA!G5+SGA!G6+SGA!G7+SGA!G8+SGA!G9+SGA!G10+SGA!G11</f>
+        <v>104562438</v>
+      </c>
+      <c r="F23" s="7">
+        <f>AVERAGE(C23:E23)</f>
+        <v>115414693.666667</v>
+      </c>
+      <c r="G23" s="7">
+        <f>AVERAGE(D23:E23)</f>
+        <v>112984767.5</v>
+      </c>
+      <c r="H23" s="18" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>運賃＋車両関連費</t>
+        </is>
+      </c>
+      <c r="C24" s="7">
+        <f>SGA!C16+SGA!C15</f>
+        <v>36022052</v>
+      </c>
+      <c r="D24" s="7">
+        <f>SGA!E16+SGA!E15</f>
+        <v>39619785</v>
+      </c>
+      <c r="E24" s="7">
+        <f>SGA!G16+SGA!G15</f>
+        <v>38858196</v>
+      </c>
+      <c r="F24" s="7">
+        <f>AVERAGE(C24:E24)</f>
+        <v>38166677.6666667</v>
+      </c>
+      <c r="G24" s="7">
+        <f>AVERAGE(D24:E24)</f>
+        <v>39238990.5</v>
+      </c>
+      <c r="H24" s="18" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>【進行期：2026年4〜7月（4か月累計）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>売上高</t>
+        </is>
+      </c>
+      <c r="C27" s="7">
+        <f>PL!I10</f>
+        <v>411154947</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>売上総利益</t>
+        </is>
+      </c>
+      <c r="C28" s="7">
+        <f>PL!I15</f>
+        <v>61213573</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>営業利益</t>
+        </is>
+      </c>
+      <c r="C29" s="7">
+        <f>PL!I17</f>
+        <v>5316980</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>減価償却費</t>
+        </is>
+      </c>
+      <c r="C30" s="7">
+        <f>SGA!I31</f>
+        <v>2436000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>経常利益</t>
+        </is>
+      </c>
+      <c r="C31" s="7">
+        <f>PL!I29</f>
+        <v>5884887</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>売上総利益率</t>
+        </is>
+      </c>
+      <c r="C32" s="15">
+        <f>IFERROR(C28/C27,"")</f>
+        <v>0.148882005303952</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>前期同期間（4〜7月）売上高：概況説明書月別</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>419288000</v>
+      </c>
+      <c r="H33" s="18" t="inlineStr">
+        <is>
+          <t>2025年4〜7月の月別売上合計（千円単位の記載を円換算）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -714,7 +2307,7 @@
         <f>'BS(借方)'!G6</f>
         <v>162087296</v>
       </c>
-      <c r="G5" s="19" t="inlineStr"/>
+      <c r="G5" s="18" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="12" t="inlineStr">
@@ -738,7 +2331,7 @@
         <f>'BS(借方)'!G7+'BS(借方)'!G8</f>
         <v>42952291</v>
       </c>
-      <c r="G6" s="19" t="inlineStr"/>
+      <c r="G6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="12" t="inlineStr">
@@ -762,7 +2355,7 @@
         <f>'BS(借方)'!G9</f>
         <v>36647736</v>
       </c>
-      <c r="G7" s="19" t="inlineStr"/>
+      <c r="G7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="5" t="inlineStr">
@@ -770,23 +2363,23 @@
           <t>流動資産計</t>
         </is>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="17">
         <f>'BS(借方)'!C16</f>
         <v>375589011</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <f>'BS(借方)'!D16</f>
         <v>303100807</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="17">
         <f>'BS(借方)'!E16</f>
         <v>249704912</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <f>'BS(借方)'!G16</f>
         <v>244250605</v>
       </c>
-      <c r="G8" s="19" t="inlineStr"/>
+      <c r="G8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="12" t="inlineStr">
@@ -810,7 +2403,7 @@
         <f>'BS(借方)'!G18+'BS(借方)'!G19+'BS(借方)'!G20</f>
         <v>103749925</v>
       </c>
-      <c r="G9" s="19" t="inlineStr"/>
+      <c r="G9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="12" t="inlineStr">
@@ -834,7 +2427,7 @@
         <f>'BS(借方)'!G24</f>
         <v>93137240</v>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>固定資産税評価額合計47,478千円（R8年度）。簿価との差は時価評価で要確認</t>
         </is>
@@ -862,7 +2455,7 @@
         <f>'BS(借方)'!G35</f>
         <v>33302569</v>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>うち庄内青果物卸売精算(有)31,993千円（FY53）</t>
         </is>
@@ -890,7 +2483,7 @@
         <f>'BS(借方)'!G36</f>
         <v>0</v>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>2026/3期に前期損益修正損として全額取崩し</t>
         </is>
@@ -918,7 +2511,7 @@
         <f>'BS(借方)'!G40</f>
         <v>476299797</v>
       </c>
-      <c r="G13" s="19" t="inlineStr"/>
+      <c r="G13" s="18" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="12" t="inlineStr">
@@ -942,7 +2535,7 @@
         <f>'BS (貸方)'!G6</f>
         <v>32102162</v>
       </c>
-      <c r="G14" s="19" t="inlineStr"/>
+      <c r="G14" s="18" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="12" t="inlineStr">
@@ -966,7 +2559,7 @@
         <f>'BS (貸方)'!G14</f>
         <v>337862000</v>
       </c>
-      <c r="G15" s="19" t="inlineStr"/>
+      <c r="G15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="12" t="inlineStr">
@@ -990,7 +2583,7 @@
         <f>'BS (貸方)'!G15</f>
         <v>8980000</v>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>取引先（仲卸・買参人等と推察）からの預り。債務類似項目</t>
         </is>
@@ -1002,23 +2595,23 @@
           <t>負債合計</t>
         </is>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="17">
         <f>'BS (貸方)'!C17</f>
         <v>559119222</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="17">
         <f>'BS (貸方)'!D17</f>
         <v>473771728</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="17">
         <f>'BS (貸方)'!E17</f>
         <v>407317523</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="17">
         <f>'BS (貸方)'!G17</f>
         <v>392542329</v>
       </c>
-      <c r="G17" s="19" t="inlineStr"/>
+      <c r="G17" s="18" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" s="10" t="inlineStr">
@@ -1042,7 +2635,7 @@
         <f>'BS (貸方)'!G22</f>
         <v>83757468</v>
       </c>
-      <c r="G18" s="19" t="inlineStr"/>
+      <c r="G18" s="18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="12" t="inlineStr">
@@ -1066,7 +2659,7 @@
         <f>IFERROR(F18/F13,"")</f>
         <v>0.175850312193184</v>
       </c>
-      <c r="G19" s="19" t="inlineStr"/>
+      <c r="G19" s="18" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" s="5" t="inlineStr">
@@ -1074,23 +2667,23 @@
           <t>ネットデット（有利子負債−現預金）</t>
         </is>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="17">
         <f>C15-C5</f>
         <v>175137368</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="17">
         <f>D15-D5</f>
         <v>174326699</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="17">
         <f>E15-E5</f>
         <v>150170923</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="17">
         <f>F15-F5</f>
         <v>175774704</v>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G20" s="18" t="inlineStr">
         <is>
           <t>預り保証金は含めず</t>
         </is>
@@ -1159,13 +2752,13 @@
           <t>合計</t>
         </is>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="17">
         <f>SUM(E23:E27)</f>
         <v>361058000</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="19" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>※金利・返済条件・担保・保証（代表者の連帯保証含む）は内訳書に記載がなく要確認。</t>
         </is>
@@ -1176,7 +2769,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1256,12 +2849,12 @@
       <c r="E5" s="7" t="n">
         <v>7194026</v>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>鶴岡市</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="18" t="inlineStr">
         <is>
           <t>食品スーパー（推察）</t>
         </is>
@@ -1282,12 +2875,12 @@
       <c r="E6" s="7" t="n">
         <v>2482212</v>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>鶴岡市</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t>青果小売（推察）</t>
         </is>
@@ -1308,12 +2901,12 @@
       <c r="E7" s="7" t="n">
         <v>1785378</v>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>長井市</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>青果卸（長井中央青果地方卸売市場）</t>
         </is>
@@ -1334,12 +2927,12 @@
       <c r="E8" s="7" t="n">
         <v>1931830</v>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>鶴岡市</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>生協</t>
         </is>
@@ -1360,12 +2953,12 @@
       <c r="E9" s="7" t="n">
         <v>1121037</v>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>鶴岡市</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>学校給食（推察）</t>
         </is>
@@ -1386,12 +2979,12 @@
       <c r="E10" s="7" t="n">
         <v>745635</v>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>三川町</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>公設庄内青果物地方卸売市場内事業者（推察）</t>
         </is>
@@ -1412,12 +3005,12 @@
       <c r="E11" s="7" t="n">
         <v>617729</v>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>名古屋市</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>生協連合会</t>
         </is>
@@ -1436,12 +3029,12 @@
         <v>886182</v>
       </c>
       <c r="E12" s="7" t="n"/>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t>愛知県豊田市</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr"/>
+      <c r="G12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="12" t="inlineStr">
@@ -1456,12 +3049,12 @@
         <v>705974</v>
       </c>
       <c r="E13" s="7" t="n"/>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>新庄市</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>青果卸（推察）</t>
         </is>
@@ -1478,12 +3071,12 @@
       </c>
       <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>仙台市</t>
         </is>
       </c>
-      <c r="G14" s="19" t="inlineStr"/>
+      <c r="G14" s="18" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="12" t="inlineStr">
@@ -1496,8 +3089,8 @@
         <v>630388</v>
       </c>
       <c r="E15" s="7" t="n"/>
-      <c r="F15" s="19" t="inlineStr"/>
-      <c r="G15" s="19" t="inlineStr"/>
+      <c r="F15" s="18" t="inlineStr"/>
+      <c r="G15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="12" t="inlineStr">
@@ -1562,7 +3155,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1642,12 +3235,12 @@
       <c r="E5" s="7" t="n">
         <v>12426183</v>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>三川町</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="18" t="inlineStr">
         <is>
           <t>青果卸（公設庄内青果物地方卸売市場）</t>
         </is>
@@ -1668,12 +3261,12 @@
       <c r="E6" s="7" t="n">
         <v>7397876</v>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>長井市</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t>青果卸</t>
         </is>
@@ -1692,12 +3285,12 @@
         <v>4495652</v>
       </c>
       <c r="E7" s="7" t="n"/>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>三川町</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>青果卸（公設庄内青果物地方卸売市場）</t>
         </is>
@@ -1718,12 +3311,12 @@
       <c r="E8" s="7" t="n">
         <v>676643</v>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>三川町</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr"/>
+      <c r="G8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="12" t="inlineStr">
@@ -1740,12 +3333,12 @@
       <c r="E9" s="7" t="n">
         <v>615054</v>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>福島県相馬市</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr"/>
+      <c r="G9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="12" t="inlineStr">
@@ -1758,12 +3351,12 @@
       <c r="E10" s="7" t="n">
         <v>707255</v>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>東京都千代田区</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>青果流通（バナナ等・推察）</t>
         </is>
@@ -1780,12 +3373,12 @@
       <c r="E11" s="7" t="n">
         <v>547560</v>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>東根市</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr"/>
+      <c r="G11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" s="12" t="inlineStr">
@@ -1850,7 +3443,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000B3041"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1909,12 +3516,12 @@
           <t>岡部 寛</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>代表取締役（本人）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="n">
+      <c r="D5" s="24" t="n">
         <v>1510</v>
       </c>
       <c r="E5" s="15">
@@ -1928,12 +3535,12 @@
           <t>岡部 一</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>取締役・代表者の兄弟</t>
         </is>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D6" s="24" t="n">
         <v>720</v>
       </c>
       <c r="E6" s="15">
@@ -1947,12 +3554,12 @@
           <t>岡部 和子</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>代表者の兄弟</t>
         </is>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="24" t="n">
         <v>500</v>
       </c>
       <c r="E7" s="15">
@@ -1966,12 +3573,12 @@
           <t>梅津 恵一</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="24" t="n">
         <v>360</v>
       </c>
       <c r="E8" s="15">
@@ -1985,12 +3592,12 @@
           <t>小野寺 則和</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>監査役</t>
         </is>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="24" t="n">
         <v>350</v>
       </c>
       <c r="E9" s="15">
@@ -2004,12 +3611,12 @@
           <t>岡部 竹古</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>取締役・代表者の配偶者</t>
         </is>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="24" t="n">
         <v>300</v>
       </c>
       <c r="E10" s="15">
@@ -2023,12 +3630,12 @@
           <t>佐藤 令子</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="24" t="n">
         <v>200</v>
       </c>
       <c r="E11" s="15">
@@ -2042,12 +3649,12 @@
           <t>菅原 圭吾</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>元常務取締役（2026年5月退任）</t>
         </is>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="24" t="n">
         <v>60</v>
       </c>
       <c r="E12" s="15">
@@ -2061,11 +3668,11 @@
           <t>合計</t>
         </is>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="25">
         <f>SUM(D5:D12)</f>
         <v>4000</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="26">
         <f>D13/D13</f>
         <v>1</v>
       </c>
@@ -2076,7 +3683,7 @@
           <t>うち岡部家（4名）</t>
         </is>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="24">
         <f>D5+D6+D7+D10</f>
         <v>3030</v>
       </c>
@@ -2097,7 +3704,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2179,12 +3786,12 @@
           <t>岡部 寛</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>常勤</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>社長</t>
         </is>
@@ -2210,12 +3817,12 @@
           <t>岡部 一</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>常勤</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>部長（代表者の兄弟）</t>
         </is>
@@ -2241,12 +3848,12 @@
           <t>岡部 竹古</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>非常勤</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>代表者の配偶者</t>
         </is>
@@ -2272,12 +3879,12 @@
           <t>小野寺 則和</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>非常勤</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>会計監査限定</t>
         </is>
@@ -2303,12 +3910,12 @@
           <t>菅原 圭吾</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>常勤</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>2026年5月29日退任</t>
         </is>
@@ -2354,7 +3961,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2456,1012 +4063,1012 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>野菜営業部</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>副部長</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="G5" s="24" t="n">
+      <c r="G5" s="27" t="n">
         <v>63</v>
       </c>
-      <c r="H5" s="24" t="n">
+      <c r="H5" s="27" t="n">
         <v>2025</v>
       </c>
-      <c r="I5" s="24" t="n">
+      <c r="I5" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="J5" s="28" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr"/>
-      <c r="L5" s="25" t="inlineStr"/>
-      <c r="M5" s="25" t="inlineStr"/>
+      <c r="K5" s="28" t="inlineStr"/>
+      <c r="L5" s="28" t="inlineStr"/>
+      <c r="M5" s="28" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>野菜営業部</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>副部長</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="F6" s="25" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="G6" s="24" t="n">
+      <c r="G6" s="27" t="n">
         <v>47</v>
       </c>
-      <c r="H6" s="24" t="n">
+      <c r="H6" s="27" t="n">
         <v>2002</v>
       </c>
-      <c r="I6" s="24" t="n">
+      <c r="I6" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="J6" s="25" t="inlineStr">
+      <c r="J6" s="28" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="K6" s="25" t="inlineStr">
+      <c r="K6" s="28" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="L6" s="25" t="inlineStr">
+      <c r="L6" s="28" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="M6" s="25" t="inlineStr"/>
+      <c r="M6" s="28" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>近郷部</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>課長</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="F7" s="25" t="inlineStr">
+      <c r="F7" s="28" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="G7" s="24" t="n">
+      <c r="G7" s="27" t="n">
         <v>31</v>
       </c>
-      <c r="H7" s="24" t="n">
+      <c r="H7" s="27" t="n">
         <v>2014</v>
       </c>
-      <c r="I7" s="24" t="n">
+      <c r="I7" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="J7" s="25" t="inlineStr">
+      <c r="J7" s="28" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="K7" s="25" t="inlineStr">
+      <c r="K7" s="28" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="L7" s="25" t="inlineStr">
+      <c r="L7" s="28" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="M7" s="25" t="inlineStr"/>
+      <c r="M7" s="28" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="B8" s="24" t="n">
+      <c r="B8" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>近郷部</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr"/>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr"/>
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="F8" s="25" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="G8" s="24" t="n">
+      <c r="G8" s="27" t="n">
         <v>42</v>
       </c>
-      <c r="H8" s="24" t="n">
+      <c r="H8" s="27" t="n">
         <v>2019</v>
       </c>
-      <c r="I8" s="24" t="n">
+      <c r="I8" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="25" t="inlineStr">
+      <c r="J8" s="28" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="K8" s="25" t="inlineStr"/>
-      <c r="L8" s="25" t="inlineStr">
+      <c r="K8" s="28" t="inlineStr"/>
+      <c r="L8" s="28" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="M8" s="25" t="inlineStr"/>
+      <c r="M8" s="28" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="B9" s="24" t="n">
+      <c r="B9" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>近郷部</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr"/>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr"/>
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="F9" s="25" t="inlineStr">
+      <c r="F9" s="28" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="G9" s="24" t="n">
+      <c r="G9" s="27" t="n">
         <v>45</v>
       </c>
-      <c r="H9" s="24" t="n">
+      <c r="H9" s="27" t="n">
         <v>2019</v>
       </c>
-      <c r="I9" s="24" t="n">
+      <c r="I9" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="J9" s="25" t="inlineStr">
+      <c r="J9" s="28" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="K9" s="25" t="inlineStr"/>
-      <c r="L9" s="25" t="inlineStr">
+      <c r="K9" s="28" t="inlineStr"/>
+      <c r="L9" s="28" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="M9" s="25" t="inlineStr"/>
+      <c r="M9" s="28" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" s="24" t="n">
+      <c r="B10" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>集配部</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr"/>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr"/>
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="F10" s="25" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="G10" s="24" t="n">
+      <c r="G10" s="27" t="n">
         <v>63</v>
       </c>
-      <c r="H10" s="24" t="n">
+      <c r="H10" s="27" t="n">
         <v>2020</v>
       </c>
-      <c r="I10" s="24" t="n">
+      <c r="I10" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="J10" s="25" t="inlineStr">
+      <c r="J10" s="28" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="K10" s="25" t="inlineStr"/>
-      <c r="L10" s="25" t="inlineStr">
+      <c r="K10" s="28" t="inlineStr"/>
+      <c r="L10" s="28" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="M10" s="25" t="inlineStr"/>
+      <c r="M10" s="28" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="B11" s="24" t="n">
+      <c r="B11" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>野菜営業部</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr"/>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="D11" s="28" t="inlineStr"/>
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="28" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="G11" s="24" t="n">
+      <c r="G11" s="27" t="n">
         <v>32</v>
       </c>
-      <c r="H11" s="24" t="n">
+      <c r="H11" s="27" t="n">
         <v>2020</v>
       </c>
-      <c r="I11" s="24" t="n">
+      <c r="I11" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="J11" s="25" t="inlineStr">
+      <c r="J11" s="28" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="K11" s="25" t="inlineStr"/>
-      <c r="L11" s="25" t="inlineStr">
+      <c r="K11" s="28" t="inlineStr"/>
+      <c r="L11" s="28" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="M11" s="25" t="inlineStr"/>
+      <c r="M11" s="28" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="B12" s="24" t="n">
+      <c r="B12" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>果実営業部</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr"/>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr"/>
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="F12" s="25" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="G12" s="24" t="n">
+      <c r="G12" s="27" t="n">
         <v>36</v>
       </c>
-      <c r="H12" s="24" t="n">
+      <c r="H12" s="27" t="n">
         <v>2021</v>
       </c>
-      <c r="I12" s="24" t="n">
+      <c r="I12" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="J12" s="25" t="inlineStr">
+      <c r="J12" s="28" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="K12" s="25" t="inlineStr"/>
-      <c r="L12" s="25" t="inlineStr">
+      <c r="K12" s="28" t="inlineStr"/>
+      <c r="L12" s="28" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="M12" s="25" t="inlineStr"/>
+      <c r="M12" s="28" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>集配部</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr"/>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr"/>
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="F13" s="25" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="G13" s="24" t="n">
+      <c r="G13" s="27" t="n">
         <v>42</v>
       </c>
-      <c r="H13" s="24" t="n">
+      <c r="H13" s="27" t="n">
         <v>2012</v>
       </c>
-      <c r="I13" s="24" t="n">
+      <c r="I13" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="J13" s="25" t="inlineStr">
+      <c r="J13" s="28" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="K13" s="25" t="inlineStr"/>
-      <c r="L13" s="25" t="inlineStr">
+      <c r="K13" s="28" t="inlineStr"/>
+      <c r="L13" s="28" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="M13" s="25" t="inlineStr">
+      <c r="M13" s="28" t="inlineStr">
         <is>
           <t>2022年4月よりフルタイム</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="24" t="n">
+      <c r="B14" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>生花部</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr"/>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr"/>
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>嘱託社員</t>
         </is>
       </c>
-      <c r="F14" s="25" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="G14" s="24" t="n">
+      <c r="G14" s="27" t="n">
         <v>69</v>
       </c>
-      <c r="H14" s="24" t="n">
+      <c r="H14" s="27" t="n">
         <v>2006</v>
       </c>
-      <c r="I14" s="24" t="n">
+      <c r="I14" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="J14" s="25" t="inlineStr">
+      <c r="J14" s="28" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="K14" s="25" t="inlineStr"/>
-      <c r="L14" s="25" t="inlineStr">
+      <c r="K14" s="28" t="inlineStr"/>
+      <c r="L14" s="28" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="M14" s="25" t="inlineStr"/>
+      <c r="M14" s="28" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="B15" s="24" t="n">
+      <c r="B15" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>集配部</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr"/>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr"/>
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>再雇用正社員</t>
         </is>
       </c>
-      <c r="F15" s="25" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="G15" s="24" t="n">
+      <c r="G15" s="27" t="n">
         <v>40</v>
       </c>
-      <c r="H15" s="24" t="n">
+      <c r="H15" s="27" t="n">
         <v>2023</v>
       </c>
-      <c r="I15" s="24" t="n">
+      <c r="I15" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="J15" s="25" t="inlineStr">
+      <c r="J15" s="28" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="K15" s="25" t="inlineStr"/>
-      <c r="L15" s="25" t="inlineStr"/>
-      <c r="M15" s="25" t="inlineStr"/>
+      <c r="K15" s="28" t="inlineStr"/>
+      <c r="L15" s="28" t="inlineStr"/>
+      <c r="M15" s="28" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="B16" s="24" t="n">
+      <c r="B16" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="28" t="inlineStr">
         <is>
           <t>近郷部</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr"/>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="D16" s="28" t="inlineStr"/>
+      <c r="E16" s="28" t="inlineStr">
         <is>
           <t>試用期間</t>
         </is>
       </c>
-      <c r="F16" s="25" t="inlineStr">
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="G16" s="24" t="n">
+      <c r="G16" s="27" t="n">
         <v>66</v>
       </c>
-      <c r="H16" s="24" t="n">
+      <c r="H16" s="27" t="n">
         <v>2024</v>
       </c>
-      <c r="I16" s="24" t="n">
+      <c r="I16" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="J16" s="25" t="inlineStr">
+      <c r="J16" s="28" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="K16" s="25" t="inlineStr">
+      <c r="K16" s="28" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="L16" s="25" t="inlineStr"/>
-      <c r="M16" s="25" t="inlineStr"/>
+      <c r="L16" s="28" t="inlineStr"/>
+      <c r="M16" s="28" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="B17" s="24" t="n">
+      <c r="B17" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>集配部</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr"/>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="D17" s="28" t="inlineStr"/>
+      <c r="E17" s="28" t="inlineStr">
         <is>
           <t>アルバイト</t>
         </is>
       </c>
-      <c r="F17" s="25" t="inlineStr">
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="G17" s="24" t="n">
+      <c r="G17" s="27" t="n">
         <v>55</v>
       </c>
-      <c r="H17" s="24" t="n">
+      <c r="H17" s="27" t="n">
         <v>2026</v>
       </c>
-      <c r="I17" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="25" t="inlineStr">
+      <c r="I17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="28" t="inlineStr">
         <is>
           <t>休日のみ配送</t>
         </is>
       </c>
-      <c r="K17" s="25" t="inlineStr"/>
-      <c r="L17" s="25" t="inlineStr"/>
-      <c r="M17" s="25" t="inlineStr"/>
+      <c r="K17" s="28" t="inlineStr"/>
+      <c r="L17" s="28" t="inlineStr"/>
+      <c r="M17" s="28" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="B18" s="24" t="n">
+      <c r="B18" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>総務部</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="28" t="inlineStr">
         <is>
           <t>部長</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="F18" s="25" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="G18" s="24" t="n">
+      <c r="G18" s="27" t="n">
         <v>56</v>
       </c>
-      <c r="H18" s="24" t="n">
+      <c r="H18" s="27" t="n">
         <v>1988</v>
       </c>
-      <c r="I18" s="24" t="n">
+      <c r="I18" s="27" t="n">
         <v>38</v>
       </c>
-      <c r="J18" s="25" t="inlineStr">
+      <c r="J18" s="28" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="K18" s="25" t="inlineStr"/>
-      <c r="L18" s="25" t="inlineStr"/>
-      <c r="M18" s="25" t="inlineStr"/>
+      <c r="K18" s="28" t="inlineStr"/>
+      <c r="L18" s="28" t="inlineStr"/>
+      <c r="M18" s="28" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="B19" s="24" t="n">
+      <c r="B19" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="C19" s="25" t="inlineStr">
+      <c r="C19" s="28" t="inlineStr">
         <is>
           <t>資材部</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
+      <c r="D19" s="28" t="inlineStr">
         <is>
           <t>課長</t>
         </is>
       </c>
-      <c r="E19" s="25" t="inlineStr">
+      <c r="E19" s="28" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="F19" s="25" t="inlineStr">
+      <c r="F19" s="28" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="G19" s="24" t="n">
+      <c r="G19" s="27" t="n">
         <v>65</v>
       </c>
-      <c r="H19" s="24" t="n">
+      <c r="H19" s="27" t="n">
         <v>1979</v>
       </c>
-      <c r="I19" s="24" t="n">
+      <c r="I19" s="27" t="n">
         <v>47</v>
       </c>
-      <c r="J19" s="25" t="inlineStr">
+      <c r="J19" s="28" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="K19" s="25" t="inlineStr"/>
-      <c r="L19" s="25" t="inlineStr"/>
-      <c r="M19" s="25" t="inlineStr">
+      <c r="K19" s="28" t="inlineStr"/>
+      <c r="L19" s="28" t="inlineStr"/>
+      <c r="M19" s="28" t="inlineStr">
         <is>
           <t>定年後再雇用</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="24" t="n">
+      <c r="B20" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>果実営業部</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D20" s="28" t="inlineStr">
         <is>
           <t>課長</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
+      <c r="E20" s="28" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="F20" s="25" t="inlineStr">
+      <c r="F20" s="28" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="G20" s="24" t="n">
+      <c r="G20" s="27" t="n">
         <v>49</v>
       </c>
-      <c r="H20" s="24" t="n">
+      <c r="H20" s="27" t="n">
         <v>2007</v>
       </c>
-      <c r="I20" s="24" t="n">
+      <c r="I20" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="J20" s="25" t="inlineStr">
+      <c r="J20" s="28" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="K20" s="25" t="inlineStr"/>
-      <c r="L20" s="25" t="inlineStr"/>
-      <c r="M20" s="25" t="inlineStr"/>
+      <c r="K20" s="28" t="inlineStr"/>
+      <c r="L20" s="28" t="inlineStr"/>
+      <c r="M20" s="28" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="B21" s="24" t="n">
+      <c r="B21" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="C21" s="25" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>事務</t>
         </is>
       </c>
-      <c r="D21" s="25" t="inlineStr"/>
-      <c r="E21" s="25" t="inlineStr">
+      <c r="D21" s="28" t="inlineStr"/>
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="F21" s="25" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="G21" s="24" t="n">
+      <c r="G21" s="27" t="n">
         <v>28</v>
       </c>
-      <c r="H21" s="24" t="n">
+      <c r="H21" s="27" t="n">
         <v>2019</v>
       </c>
-      <c r="I21" s="24" t="n">
+      <c r="I21" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="J21" s="25" t="inlineStr">
+      <c r="J21" s="28" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="K21" s="25" t="inlineStr"/>
-      <c r="L21" s="25" t="inlineStr"/>
-      <c r="M21" s="25" t="inlineStr"/>
+      <c r="K21" s="28" t="inlineStr"/>
+      <c r="L21" s="28" t="inlineStr"/>
+      <c r="M21" s="28" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="B22" s="24" t="n">
+      <c r="B22" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="C22" s="25" t="inlineStr">
+      <c r="C22" s="28" t="inlineStr">
         <is>
           <t>パッケージ部</t>
         </is>
       </c>
-      <c r="D22" s="25" t="inlineStr">
+      <c r="D22" s="28" t="inlineStr">
         <is>
           <t>係長</t>
         </is>
       </c>
-      <c r="E22" s="25" t="inlineStr">
+      <c r="E22" s="28" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="F22" s="25" t="inlineStr">
+      <c r="F22" s="28" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="G22" s="24" t="n">
+      <c r="G22" s="27" t="n">
         <v>52</v>
       </c>
-      <c r="H22" s="24" t="n">
+      <c r="H22" s="27" t="n">
         <v>2006</v>
       </c>
-      <c r="I22" s="24" t="n">
+      <c r="I22" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="J22" s="25" t="inlineStr">
+      <c r="J22" s="28" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="K22" s="25" t="inlineStr"/>
-      <c r="L22" s="25" t="inlineStr"/>
-      <c r="M22" s="25" t="inlineStr">
+      <c r="K22" s="28" t="inlineStr"/>
+      <c r="L22" s="28" t="inlineStr"/>
+      <c r="M22" s="28" t="inlineStr">
         <is>
           <t>2012年4月よりフルタイム</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="24" t="n">
+      <c r="B23" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="C23" s="25" t="inlineStr">
+      <c r="C23" s="28" t="inlineStr">
         <is>
           <t>パッケージ部</t>
         </is>
       </c>
-      <c r="D23" s="25" t="inlineStr"/>
-      <c r="E23" s="25" t="inlineStr">
+      <c r="D23" s="28" t="inlineStr"/>
+      <c r="E23" s="28" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="F23" s="25" t="inlineStr">
+      <c r="F23" s="28" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="G23" s="24" t="n">
+      <c r="G23" s="27" t="n">
         <v>65</v>
       </c>
-      <c r="H23" s="24" t="n">
+      <c r="H23" s="27" t="n">
         <v>2006</v>
       </c>
-      <c r="I23" s="24" t="n">
+      <c r="I23" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="J23" s="25" t="inlineStr">
+      <c r="J23" s="28" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="K23" s="25" t="inlineStr"/>
-      <c r="L23" s="25" t="inlineStr"/>
-      <c r="M23" s="25" t="inlineStr">
+      <c r="K23" s="28" t="inlineStr"/>
+      <c r="L23" s="28" t="inlineStr"/>
+      <c r="M23" s="28" t="inlineStr">
         <is>
           <t>2012年4月よりフルタイム／定年後再雇用</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="24" t="n">
+      <c r="B24" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>パッケージ部</t>
         </is>
       </c>
-      <c r="D24" s="25" t="inlineStr"/>
-      <c r="E24" s="25" t="inlineStr">
+      <c r="D24" s="28" t="inlineStr"/>
+      <c r="E24" s="28" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="F24" s="25" t="inlineStr">
+      <c r="F24" s="28" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="G24" s="24" t="n">
+      <c r="G24" s="27" t="n">
         <v>55</v>
       </c>
-      <c r="H24" s="24" t="n">
+      <c r="H24" s="27" t="n">
         <v>2021</v>
       </c>
-      <c r="I24" s="24" t="n">
+      <c r="I24" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="J24" s="25" t="inlineStr">
+      <c r="J24" s="28" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="K24" s="25" t="inlineStr"/>
-      <c r="L24" s="25" t="inlineStr"/>
-      <c r="M24" s="25" t="inlineStr"/>
+      <c r="K24" s="28" t="inlineStr"/>
+      <c r="L24" s="28" t="inlineStr"/>
+      <c r="M24" s="28" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="B25" s="24" t="n">
+      <c r="B25" s="27" t="n">
         <v>21</v>
       </c>
-      <c r="C25" s="25" t="inlineStr">
+      <c r="C25" s="28" t="inlineStr">
         <is>
           <t>パッケージ部</t>
         </is>
       </c>
-      <c r="D25" s="25" t="inlineStr"/>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="D25" s="28" t="inlineStr"/>
+      <c r="E25" s="28" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="F25" s="25" t="inlineStr">
+      <c r="F25" s="28" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="G25" s="24" t="n">
+      <c r="G25" s="27" t="n">
         <v>65</v>
       </c>
-      <c r="H25" s="24" t="n">
+      <c r="H25" s="27" t="n">
         <v>2009</v>
       </c>
-      <c r="I25" s="24" t="n">
+      <c r="I25" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="J25" s="25" t="inlineStr">
+      <c r="J25" s="28" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="K25" s="25" t="inlineStr"/>
-      <c r="L25" s="25" t="inlineStr"/>
-      <c r="M25" s="25" t="inlineStr">
+      <c r="K25" s="28" t="inlineStr"/>
+      <c r="L25" s="28" t="inlineStr"/>
+      <c r="M25" s="28" t="inlineStr">
         <is>
           <t>2012年4月よりフルタイム</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="24" t="n">
+      <c r="B26" s="27" t="n">
         <v>22</v>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="28" t="inlineStr">
         <is>
           <t>パッケージ部</t>
         </is>
       </c>
-      <c r="D26" s="25" t="inlineStr"/>
-      <c r="E26" s="25" t="inlineStr">
+      <c r="D26" s="28" t="inlineStr"/>
+      <c r="E26" s="28" t="inlineStr">
         <is>
           <t>パート</t>
         </is>
       </c>
-      <c r="F26" s="25" t="inlineStr">
+      <c r="F26" s="28" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="G26" s="24" t="n">
+      <c r="G26" s="27" t="n">
         <v>67</v>
       </c>
-      <c r="H26" s="24" t="n">
+      <c r="H26" s="27" t="n">
         <v>2012</v>
       </c>
-      <c r="I26" s="24" t="n">
+      <c r="I26" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="J26" s="25" t="inlineStr">
+      <c r="J26" s="28" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="K26" s="25" t="inlineStr"/>
-      <c r="L26" s="25" t="inlineStr"/>
-      <c r="M26" s="25" t="inlineStr"/>
+      <c r="K26" s="28" t="inlineStr"/>
+      <c r="L26" s="28" t="inlineStr"/>
+      <c r="M26" s="28" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="B27" s="24" t="n">
+      <c r="B27" s="27" t="n">
         <v>23</v>
       </c>
-      <c r="C27" s="25" t="inlineStr">
+      <c r="C27" s="28" t="inlineStr">
         <is>
           <t>パッケージ部</t>
         </is>
       </c>
-      <c r="D27" s="25" t="inlineStr"/>
-      <c r="E27" s="25" t="inlineStr">
+      <c r="D27" s="28" t="inlineStr"/>
+      <c r="E27" s="28" t="inlineStr">
         <is>
           <t>パート</t>
         </is>
       </c>
-      <c r="F27" s="25" t="inlineStr">
+      <c r="F27" s="28" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="G27" s="24" t="n">
+      <c r="G27" s="27" t="n">
         <v>29</v>
       </c>
-      <c r="H27" s="24" t="n">
+      <c r="H27" s="27" t="n">
         <v>2018</v>
       </c>
-      <c r="I27" s="24" t="n">
+      <c r="I27" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="J27" s="25" t="inlineStr">
+      <c r="J27" s="28" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="K27" s="25" t="inlineStr"/>
-      <c r="L27" s="25" t="inlineStr"/>
-      <c r="M27" s="25" t="inlineStr"/>
+      <c r="K27" s="28" t="inlineStr"/>
+      <c r="L27" s="28" t="inlineStr"/>
+      <c r="M27" s="28" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="B28" s="24" t="n">
+      <c r="B28" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="C28" s="25" t="inlineStr">
+      <c r="C28" s="28" t="inlineStr">
         <is>
           <t>パッケージ部</t>
         </is>
       </c>
-      <c r="D28" s="25" t="inlineStr"/>
-      <c r="E28" s="25" t="inlineStr">
+      <c r="D28" s="28" t="inlineStr"/>
+      <c r="E28" s="28" t="inlineStr">
         <is>
           <t>パート</t>
         </is>
       </c>
-      <c r="F28" s="25" t="inlineStr">
+      <c r="F28" s="28" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="G28" s="24" t="n">
+      <c r="G28" s="27" t="n">
         <v>59</v>
       </c>
-      <c r="H28" s="24" t="n">
+      <c r="H28" s="27" t="n">
         <v>2023</v>
       </c>
-      <c r="I28" s="24" t="n">
+      <c r="I28" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="J28" s="25" t="inlineStr">
+      <c r="J28" s="28" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="K28" s="25" t="inlineStr"/>
-      <c r="L28" s="25" t="inlineStr"/>
-      <c r="M28" s="25" t="inlineStr"/>
+      <c r="K28" s="28" t="inlineStr"/>
+      <c r="L28" s="28" t="inlineStr"/>
+      <c r="M28" s="28" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="B30" s="20" t="inlineStr">
@@ -3482,7 +5089,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3522,7 +5129,7 @@
           <t>本社・市場</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>山形県鶴岡市宝田一丁目4番20号（宝田一丁目4-2：宅地3,100.22㎡。事務所・市場・倉庫・貯蔵庫。自社所有）</t>
         </is>
@@ -3534,7 +5141,7 @@
           <t>パッケージ場・倉庫</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>鶴岡市宝田一丁目5-1（宅地900.50㎡。事務所兼倉庫〔パッケージ場〕629.34㎡・倉庫139.08㎡。自社所有）</t>
         </is>
@@ -3546,7 +5153,7 @@
           <t>倉庫敷地</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>東田川郡庄内町長沼字宮前304-7（宅地261.81㎡。自社所有。建物の課税明細なし＝建物の有無は要確認）</t>
         </is>
@@ -3558,7 +5165,7 @@
           <t>賃借物件</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>なし（地代家賃の計上なし）。ただしリース料年6,227千円（車両・冷蔵設備等と推察、要確認）</t>
         </is>
@@ -3569,7 +5176,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3644,17 +5251,17 @@
           <t>鶴岡市宝田一丁目4-2</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>宅地</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>市場・事務所・倉庫</t>
         </is>
       </c>
-      <c r="E5" s="26" t="n">
+      <c r="E5" s="29" t="n">
         <v>3100.22</v>
       </c>
       <c r="F5" s="7" t="n">
@@ -3670,17 +5277,17 @@
           <t>鶴岡市宝田一丁目5-1</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>宅地</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>パッケージ場・倉庫</t>
         </is>
       </c>
-      <c r="E6" s="26" t="n">
+      <c r="E6" s="29" t="n">
         <v>900.5</v>
       </c>
       <c r="F6" s="7" t="n">
@@ -3696,17 +5303,17 @@
           <t>東田川郡庄内町長沼字宮前304-7</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>宅地</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>倉庫敷地</t>
         </is>
       </c>
-      <c r="E7" s="26" t="n">
+      <c r="E7" s="29" t="n">
         <v>261.81</v>
       </c>
       <c r="F7" s="7" t="n">
@@ -3722,7 +5329,7 @@
           <t>土地 計</t>
         </is>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="30">
         <f>SUM(E5:E7)</f>
         <v>4262.53</v>
       </c>
@@ -3780,25 +5387,25 @@
           <t>宝田一丁目4-2</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>事務所</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>鉄骨造 亜鉛メッキ鋼板葺</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>2階</t>
         </is>
       </c>
-      <c r="F11" s="26" t="n">
+      <c r="F11" s="29" t="n">
         <v>365.63</v>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>1981年（昭和56年）</t>
         </is>
@@ -3813,25 +5420,25 @@
           <t>宝田一丁目4-2</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>市場</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>鉄骨造 亜鉛メッキ鋼板葺</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>1階</t>
         </is>
       </c>
-      <c r="F12" s="26" t="n">
+      <c r="F12" s="29" t="n">
         <v>320.22</v>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>1981年（昭和56年）</t>
         </is>
@@ -3846,25 +5453,25 @@
           <t>宝田一丁目4-2</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>倉庫</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>鉄骨造 亜鉛メッキ鋼板葺</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>1階</t>
         </is>
       </c>
-      <c r="F13" s="26" t="n">
+      <c r="F13" s="29" t="n">
         <v>327.13</v>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>1981年（昭和56年）</t>
         </is>
@@ -3879,25 +5486,25 @@
           <t>宝田一丁目4-2</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>倉庫</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>軽量鉄骨造</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>2階</t>
         </is>
       </c>
-      <c r="F14" s="26" t="n">
+      <c r="F14" s="29" t="n">
         <v>198.74</v>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>1981年（昭和56年）</t>
         </is>
@@ -3912,25 +5519,25 @@
           <t>宝田一丁目4-2</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>貯蔵庫</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>軽量鉄骨造</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>1階</t>
         </is>
       </c>
-      <c r="F15" s="26" t="n">
+      <c r="F15" s="29" t="n">
         <v>34.48</v>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>1981年（昭和56年）</t>
         </is>
@@ -3945,25 +5552,25 @@
           <t>宝田一丁目5-1</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>事務所兼倉庫</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>鉄骨造 亜鉛メッキ鋼板葺</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>2階</t>
         </is>
       </c>
-      <c r="F16" s="26" t="n">
+      <c r="F16" s="29" t="n">
         <v>627.4</v>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>1982年（昭和57年）</t>
         </is>
@@ -3978,25 +5585,25 @@
           <t>宝田一丁目5-1</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>倉庫</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>鉄骨造 亜鉛メッキ鋼板葺</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>1階</t>
         </is>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="29" t="n">
         <v>139.08</v>
       </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>2012年（平成24年）</t>
         </is>
@@ -4011,7 +5618,7 @@
           <t>建物 計</t>
         </is>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="30">
         <f>SUM(F11:F17)</f>
         <v>2012.68</v>
       </c>
@@ -4046,13 +5653,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -4103,7 +5710,7 @@
         <f>'BS(借方)'!E19</f>
         <v>11399836</v>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>冷蔵庫ユニット交換・シャッター更新等（内訳書記載の改修工事）</t>
         </is>
@@ -4119,7 +5726,7 @@
         <f>'BS(借方)'!E20</f>
         <v>284395</v>
       </c>
-      <c r="D6" s="19" t="inlineStr"/>
+      <c r="D6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="12" t="inlineStr">
@@ -4131,7 +5738,7 @@
         <f>'BS(借方)'!E21</f>
         <v>2</v>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>備忘価額のみ（償却済）</t>
         </is>
@@ -4147,7 +5754,7 @@
         <f>'BS(借方)'!E22</f>
         <v>15</v>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>備忘価額のみ。集配車両はリースと推察（要確認）</t>
         </is>
@@ -4163,7 +5770,7 @@
         <f>'BS(借方)'!E23</f>
         <v>18546</v>
       </c>
-      <c r="D9" s="19" t="inlineStr"/>
+      <c r="D9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="12" t="inlineStr">
@@ -4175,10 +5782,440 @@
         <f>'BS(借方)'!E29</f>
         <v>371800</v>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>販売管理システム等と推察（要確認）</t>
         </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>建物内訳（用途）</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>簿価(2026/3末)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>所在・面積</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>管理棟</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>20192827</v>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20／365.00㎡</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>荷捌市場</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>5899377</v>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20／330.70㎡</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>倉庫</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>1165921</v>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20／320.20㎡</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>容器庫</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>500001</v>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20／198.70㎡</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>物置</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20／34.40㎡</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>容器倉庫</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>249260</v>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>シャッター</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>シャッター取替</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>1739340</v>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>改修工事</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>2695280</v>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>改修工事</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>6000156</v>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>パッケージ場</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>11751239</v>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目5-20／629.34㎡</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>シャッター更新</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>1077501</v>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>プレハブ修繕</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>1377441</v>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>不用材置場</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>倉庫</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>8917430</v>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目5-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>2階改修</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>6403541</v>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>1階トイレ改修</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>1169632</v>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>屋根改修</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>3391200</v>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>屋根改修</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>3120320</v>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>屋根改修</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>3736745</v>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>下屋修理・塗装</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>971487</v>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>パッケージ場外壁</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>6815160</v>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目5-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>冷蔵庫ユニット交換工事</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>1001990</v>
+      </c>
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>シャッター</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>2570350</v>
+      </c>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>資材倉庫外壁改修（2025年5月）</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>917734</v>
+      </c>
+      <c r="D37" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>資材倉庫シャッター（2025年5月）</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>401759</v>
+      </c>
+      <c r="D38" s="18" t="inlineStr">
+        <is>
+          <t>宝田一丁目4-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>建物 計</t>
+        </is>
+      </c>
+      <c r="C39" s="9">
+        <f>SUM(C13:C38)</f>
+        <v>92065694</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>チェック：BS建物と一致</t>
+        </is>
+      </c>
+      <c r="C40" t="b">
+        <f>EXACT(C39,'BS(借方)'!E18)</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4186,7 +6223,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4305,43 +6342,43 @@
           <t>売上高</t>
         </is>
       </c>
-      <c r="C5" s="21" t="n">
+      <c r="C5" s="24" t="n">
         <v>87736</v>
       </c>
-      <c r="D5" s="21" t="n">
+      <c r="D5" s="24" t="n">
         <v>101698</v>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="E5" s="24" t="n">
         <v>83794</v>
       </c>
-      <c r="F5" s="21" t="n">
+      <c r="F5" s="24" t="n">
         <v>146060</v>
       </c>
-      <c r="G5" s="21" t="n">
+      <c r="G5" s="24" t="n">
         <v>138177</v>
       </c>
-      <c r="H5" s="21" t="n">
+      <c r="H5" s="24" t="n">
         <v>110175</v>
       </c>
-      <c r="I5" s="21" t="n">
+      <c r="I5" s="24" t="n">
         <v>106499</v>
       </c>
-      <c r="J5" s="21" t="n">
+      <c r="J5" s="24" t="n">
         <v>100617</v>
       </c>
-      <c r="K5" s="21" t="n">
+      <c r="K5" s="24" t="n">
         <v>98058</v>
       </c>
-      <c r="L5" s="21" t="n">
+      <c r="L5" s="24" t="n">
         <v>69520</v>
       </c>
-      <c r="M5" s="21" t="n">
+      <c r="M5" s="24" t="n">
         <v>69339</v>
       </c>
-      <c r="N5" s="21" t="n">
+      <c r="N5" s="24" t="n">
         <v>84221</v>
       </c>
-      <c r="O5" s="28">
+      <c r="O5" s="31">
         <f>SUM(C5:N5)</f>
         <v>1195894</v>
       </c>
@@ -4352,43 +6389,43 @@
           <t>仕入高</t>
         </is>
       </c>
-      <c r="C6" s="21" t="n">
+      <c r="C6" s="24" t="n">
         <v>76904</v>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D6" s="24" t="n">
         <v>86235</v>
       </c>
-      <c r="E6" s="21" t="n">
+      <c r="E6" s="24" t="n">
         <v>74095</v>
       </c>
-      <c r="F6" s="21" t="n">
+      <c r="F6" s="24" t="n">
         <v>139243</v>
       </c>
-      <c r="G6" s="21" t="n">
+      <c r="G6" s="24" t="n">
         <v>96826</v>
       </c>
-      <c r="H6" s="21" t="n">
+      <c r="H6" s="24" t="n">
         <v>85074</v>
       </c>
-      <c r="I6" s="21" t="n">
+      <c r="I6" s="24" t="n">
         <v>84386</v>
       </c>
-      <c r="J6" s="21" t="n">
+      <c r="J6" s="24" t="n">
         <v>85425</v>
       </c>
-      <c r="K6" s="21" t="n">
+      <c r="K6" s="24" t="n">
         <v>82345</v>
       </c>
-      <c r="L6" s="21" t="n">
+      <c r="L6" s="24" t="n">
         <v>56698</v>
       </c>
-      <c r="M6" s="21" t="n">
+      <c r="M6" s="24" t="n">
         <v>58088</v>
       </c>
-      <c r="N6" s="21" t="n">
+      <c r="N6" s="24" t="n">
         <v>70716</v>
       </c>
-      <c r="O6" s="28">
+      <c r="O6" s="31">
         <f>SUM(C6:N6)</f>
         <v>996035</v>
       </c>
@@ -4399,43 +6436,43 @@
           <t>人件費</t>
         </is>
       </c>
-      <c r="C7" s="21" t="n">
+      <c r="C7" s="24" t="n">
         <v>4204</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="24" t="n">
         <v>7349</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="24" t="n">
         <v>7586</v>
       </c>
-      <c r="F7" s="21" t="n">
+      <c r="F7" s="24" t="n">
         <v>7363</v>
       </c>
-      <c r="G7" s="21" t="n">
+      <c r="G7" s="24" t="n">
         <v>7717</v>
       </c>
-      <c r="H7" s="21" t="n">
+      <c r="H7" s="24" t="n">
         <v>7474</v>
       </c>
-      <c r="I7" s="21" t="n">
+      <c r="I7" s="24" t="n">
         <v>7291</v>
       </c>
-      <c r="J7" s="21" t="n">
+      <c r="J7" s="24" t="n">
         <v>7298</v>
       </c>
-      <c r="K7" s="21" t="n">
+      <c r="K7" s="24" t="n">
         <v>7200</v>
       </c>
-      <c r="L7" s="21" t="n">
+      <c r="L7" s="24" t="n">
         <v>6903</v>
       </c>
-      <c r="M7" s="21" t="n">
+      <c r="M7" s="24" t="n">
         <v>6884</v>
       </c>
-      <c r="N7" s="21" t="n">
+      <c r="N7" s="24" t="n">
         <v>9764</v>
       </c>
-      <c r="O7" s="28">
+      <c r="O7" s="31">
         <f>SUM(C7:N7)</f>
         <v>87033</v>
       </c>
@@ -4445,21 +6482,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="000B3041"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4506,400 +6529,400 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="29" t="n">
+      <c r="B4" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>事業</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>売上高の構成（買付販売／受託販売手数料／センター費／資材・肥料売上）の年度別内訳。決算書では「商品売上高」1本表示</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>事業</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>市場の法的位置づけ（卸売市場法上の地方卸売市場の認定／開設者兼卸売業者）、認定日・条件、仲卸業者数・売買参加者数</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="29" t="n">
+      <c r="B6" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>事業</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>主要販売先別・仕入先（出荷者）別の年間取引高（内訳書は期末残高のみ）。(株)主婦の店への依存度</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>事業</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>「主婦センター費」「センター費」の内容（主婦の店の物流センター業務の受託と推察）、契約条件</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="29" t="n">
+      <c r="B8" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>財務</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>2025/3期の営業赤字（△4,423千円）の要因。売上総利益率は18.6%→17.9%→16.6%と低下</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>財務</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>2026/3期に賞与計上がない理由。今後の支給方針</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="29" t="n">
+      <c r="B10" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>財務</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>前期損益修正損20,900千円（過年度保険解約訂正額）の経緯。解約返戻金の受領有無</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="29" t="n">
+      <c r="B11" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>財務</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>役員報酬の減額（代表者10,560千円→4,320千円）の理由、常務取締役退任（2026/5）後の体制</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="29" t="n">
+      <c r="B12" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>財務</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>借入金の金利・返済予定・担保・代表者保証。有利子負債361,058千円（2026/3末）</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>財務</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>保証金31,993千円（庄内青果物卸売精算(有)）の性質・返還条件、預り保証金8,980千円の相手先</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="29" t="n">
+      <c r="B14" s="32" t="n">
         <v>11</v>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>財務</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>投資有価証券の減少（2026/3末2,600千円→2026/7末1,600千円）。(株)庄果株式の処分有無</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>財務</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>租税公課12,177千円の内訳（税込経理による消費税納付額と推察）</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="32" t="n">
         <v>13</v>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>不動産</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>土地の時価（簿価93,137千円／固定資産税評価額47,478千円）。建物の耐震性・修繕計画</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="29" t="n">
+      <c r="B17" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>不動産</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>庄内町長沼の倉庫敷地の利用状況（建物の有無）</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="29" t="n">
+      <c r="B18" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>人事</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>従業員数の定義差（名簿24名／概況説明書30名／県資料40名）。セリ人・キーパーソン、後継体制</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="29" t="n">
+      <c r="B19" s="32" t="n">
         <v>16</v>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>人事</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>就業規則・退職金規程（退職金共済加入のみか）・未払残業代の有無</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="29" t="n">
+      <c r="B20" s="32" t="n">
         <v>17</v>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>会社HP（turu-chu.co.jp）で「だだちゃ豆」「庄内柿」「和梨・洋梨の特別栽培」等を紹介（検索結果の要約。ネットワーク制限により本文未閲覧：要確認）</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="29" t="n">
+      <c r="B21" s="32" t="n">
         <v>18</v>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>山形県「地方卸売市場の概要」に鶴岡中央青果（開設者兼卸売業者）が掲載。従業員40名・開設時期の記載あり（本文未閲覧：要確認）</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="29" t="n">
+      <c r="B22" s="32" t="n">
         <v>19</v>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>近隣には公設庄内青果物地方卸売市場（三川町、庄内広域行政組合開設）があり、仕入先の丸果庄内青果(株)・(株)庄果が入場</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="29" t="n">
+      <c r="B23" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>譲渡条件</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>スキーム（株式譲渡100%を想定）、希望価格、役員の継続関与、従業員の雇用維持、譲渡理由</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -8849,223 +10872,423 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="64" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>会社概要（基本情報ページの原本）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="4" t="inlineStr"/>
-      <c r="B3" s="4" t="inlineStr">
+          <t>修正PL（正常収益力の算定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>単位：千円（入力は円）。営業利益ベースで調整。概要書の調整後EBITDAも本シートを参照する</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>商号</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>株式会社鶴岡中央青果</t>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>2024年3月期
+(第51期)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>2025年3月期
+(第52期)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>2026年3月期
+(第53期)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>調整事由</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>本店所在地</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>山形県鶴岡市宝田一丁目4番20号</t>
-        </is>
-      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>営業利益（帳簿）</t>
+        </is>
+      </c>
+      <c r="C5" s="17">
+        <f>PL!C17</f>
+        <v>4756748</v>
+      </c>
+      <c r="D5" s="17">
+        <f>PL!E17</f>
+        <v>-4422940</v>
+      </c>
+      <c r="E5" s="17">
+        <f>PL!G17</f>
+        <v>5859912</v>
+      </c>
+      <c r="F5" s="18" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>設立</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>1973年（昭和48年）11月22日</t>
-        </is>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>（前提）社会保険料率</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>代表者</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>代表取締役　岡部 寛</t>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>（前提）代表者及びその家族分の役員報酬（実績）</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>10680000</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>10680000</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>4440000</v>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>勘定科目内訳書「人件費の内訳」（代表取締役・取締役〔配偶者〕）</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>資本金</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>40,000千円</t>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>（前提）新体制の役員報酬（仮定）</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>（仮定）買手からの派遣役員等を年8,000千円と想定</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>発行済株式総数</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>4,000株（発行可能株式総数5,000株、譲渡制限あり：取締役会の承認）</t>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>①役員報酬の正常化（社保込）</t>
+        </is>
+      </c>
+      <c r="C9" s="7">
+        <f>(C7-C8)*(1+$C$6)</f>
+        <v>3082000</v>
+      </c>
+      <c r="D9" s="7">
+        <f>(D7-D8)*(1+$C$6)</f>
+        <v>3082000</v>
+      </c>
+      <c r="E9" s="7">
+        <f>(E7-E8)*(1+$C$6)</f>
+        <v>-4094000</v>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>退任予定と想定する代表者・配偶者の報酬を控除し、新体制の報酬に置換。社会保険料も概算15%で連動。常務取締役（2026/5退任）の後任要否は要確認のため対象外</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>事業内容</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>青果物（野菜・果実）の卸売（鶴岡市宝田における地方卸売市場の開設・運営および卸売業）、包装資材・肥料等の販売、パッケージ（小分け・包装）業務、倉庫業</t>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>②賞与の正常化（社保込）</t>
+        </is>
+      </c>
+      <c r="C10" s="7">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="7">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="7">
+        <f>-AVERAGE(SGA!C7,SGA!E7)*(1+$C$6)</f>
+        <v>-6724423.75</v>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>2026/3期は賞与計上なし。前2期平均相当を費用計上（仮説：支給再開を前提。不支給の経緯は要確認）</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>登記上の目的</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>1 青果物の販売及び卸売の業務　2 倉庫業　3 前号に附帯する一切の業務</t>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>③寄付金の加算</t>
+        </is>
+      </c>
+      <c r="C11" s="7">
+        <f>SGA!C26</f>
+        <v>13000</v>
+      </c>
+      <c r="D11" s="7">
+        <f>SGA!E26</f>
+        <v>71000</v>
+      </c>
+      <c r="E11" s="7">
+        <f>SGA!G26</f>
+        <v>11000</v>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>譲渡後に発生しない費用として加算</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>機関設計</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>取締役会設置会社／監査役設置会社（監査の範囲を会計に限定）</t>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>④受取奨励金（純額）の加算</t>
+        </is>
+      </c>
+      <c r="C12" s="7">
+        <f>PL!C20-PL!C26</f>
+        <v>2178508</v>
+      </c>
+      <c r="D12" s="7">
+        <f>PL!E20-PL!E26</f>
+        <v>2314707</v>
+      </c>
+      <c r="E12" s="7">
+        <f>PL!G20-PL!G26</f>
+        <v>2418448</v>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>営業外に計上されているが、仕入完納等に伴い毎期経常的に発生する事業関連収益（受取奨励金−出荷奨励金）</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>従業員数</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>職員名簿24名（うち正社員等17名・嘱託/再雇用/試用3名・パート3名・アルバイト1名）＋常勤役員2名（2026年9月1日現在）</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>修正額 計</t>
+        </is>
+      </c>
+      <c r="C13" s="17">
+        <f>SUM(C9:C12)</f>
+        <v>5273508</v>
+      </c>
+      <c r="D13" s="17">
+        <f>SUM(D9:D12)</f>
+        <v>5467707</v>
+      </c>
+      <c r="E13" s="17">
+        <f>SUM(E9:E12)</f>
+        <v>-8388975.75</v>
+      </c>
+      <c r="F13" s="18" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>決算期</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>3月</t>
-        </is>
-      </c>
+          <t>修正後営業利益</t>
+        </is>
+      </c>
+      <c r="C14" s="11">
+        <f>C5+C13</f>
+        <v>10030256</v>
+      </c>
+      <c r="D14" s="11">
+        <f>D5+D13</f>
+        <v>1044767</v>
+      </c>
+      <c r="E14" s="11">
+        <f>E5+E13</f>
+        <v>-2529063.75</v>
+      </c>
+      <c r="F14" s="18" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>営業時間／定休日</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>6時〜17時（推察。概況説明書上「開店6時・閉店5時」）／水・日・祝日</t>
-        </is>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>（前提）実効税率</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>0.34</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>主要取引金融機関</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>鶴岡信用金庫、山形銀行、荘内銀行、日本政策金融公庫</t>
-        </is>
-      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>税考慮額</t>
+        </is>
+      </c>
+      <c r="C16" s="7">
+        <f>-C14*$C$15</f>
+        <v>-3410287.04</v>
+      </c>
+      <c r="D16" s="7">
+        <f>-D14*$C$15</f>
+        <v>-355220.78</v>
+      </c>
+      <c r="E16" s="7">
+        <f>-E14*$C$15</f>
+        <v>859881.675</v>
+      </c>
+      <c r="F16" s="18" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>顧問税理士</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>池田昭一税理士事務所（山形県酒田市）</t>
-        </is>
-      </c>
+          <t>修正後税考慮後営業利益</t>
+        </is>
+      </c>
+      <c r="C17" s="11">
+        <f>C14+C16</f>
+        <v>6619968.96</v>
+      </c>
+      <c r="D17" s="11">
+        <f>D14+D16</f>
+        <v>689546.22</v>
+      </c>
+      <c r="E17" s="11">
+        <f>E14+E16</f>
+        <v>-1669182.075</v>
+      </c>
+      <c r="F17" s="18" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Webサイト</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>https://www.turu-chu.co.jp/（検索結果により存在を確認。法人事業概況説明書では「HPなし」と記載：要確認）</t>
-        </is>
-      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>減価償却費</t>
+        </is>
+      </c>
+      <c r="C18" s="7">
+        <f>SGA!C31</f>
+        <v>13663684</v>
+      </c>
+      <c r="D18" s="7">
+        <f>SGA!E31</f>
+        <v>12557564</v>
+      </c>
+      <c r="E18" s="7">
+        <f>SGA!G31</f>
+        <v>8878970</v>
+      </c>
+      <c r="F18" s="18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>直近業績(2026/3期)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>売上高 1,195,893千円／営業利益 5,859千円／経常利益 8,067千円</t>
+          <t>修正後EBITDA</t>
+        </is>
+      </c>
+      <c r="C19" s="11">
+        <f>C14+C18</f>
+        <v>23693940</v>
+      </c>
+      <c r="D19" s="11">
+        <f>D14+D18</f>
+        <v>13602331</v>
+      </c>
+      <c r="E19" s="11">
+        <f>E14+E18</f>
+        <v>6349906.25</v>
+      </c>
+      <c r="F19" s="18" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>加重（前々期：前期：直近期）</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>基準営業利益（税考慮後・加重平均）</t>
+        </is>
+      </c>
+      <c r="E21" s="9">
+        <f>SUMPRODUCT(C17:E17,C20:E20)</f>
+        <v>696266.620500001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>基準EBITDA（加重平均）</t>
+        </is>
+      </c>
+      <c r="E22" s="9">
+        <f>SUMPRODUCT(C19:E19,C20:E20)</f>
+        <v>11994440.425</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>※支払利息は営業外費用のため営業利益ベースの正常収益力には含まれない（債権者への分配前の収益として算定）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>※前期損益修正損（保険解約訂正）・固定資産売却損益・貸倒引当金繰入/戻入は特別損益のため対象外（非経常）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>※雑収入（ゴミ処理料・冷蔵庫保管料等の経常部分を含む）は内容の区分資料がないため加算していない（要確認。加算余地あり）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>※支払保険料・接待交際費にオーナー個人に帰属する費用が含まれるかは未確認（要確認）。</t>
         </is>
       </c>
     </row>
@@ -9080,30 +11303,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>財務ハイライト（P/L）・調整後EBITDA</t>
+          <t>修正BS（時価純資産の算定）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>単位：千円（入力は円）</t>
+          <t>評価基準日：2026年3月31日（2026/3期末貸借対照表）。単位：千円（入力は円）</t>
         </is>
       </c>
     </row>
@@ -9111,657 +11332,927 @@
       <c r="A4" s="4" t="inlineStr"/>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>項目</t>
+          <t>科目</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>2024年3月期
-(第51期)</t>
+          <t>帳簿価額</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2025年3月期
-(第52期)</t>
+          <t>修正額</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026年3月期
-(第53期)</t>
+          <t>修正後</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>3期平均</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>直近2期平均</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>備考</t>
+          <t>修正事由／評価方法</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>売上高</t>
-        </is>
-      </c>
-      <c r="C5" s="18">
-        <f>PL!C10</f>
-        <v>1178489098</v>
-      </c>
-      <c r="D5" s="18">
-        <f>PL!E10</f>
-        <v>1181947340</v>
-      </c>
-      <c r="E5" s="18">
-        <f>PL!G10</f>
-        <v>1195893269</v>
-      </c>
-      <c r="F5" s="18">
-        <f>AVERAGE(C5:E5)</f>
-        <v>1185443235.66667</v>
-      </c>
-      <c r="G5" s="18">
-        <f>AVERAGE(D5:E5)</f>
-        <v>1188920304.5</v>
-      </c>
-      <c r="H5" s="19" t="inlineStr"/>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>現金及び預金</t>
+        </is>
+      </c>
+      <c r="C5" s="7">
+        <f>'BS(借方)'!E6</f>
+        <v>210887077</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7">
+        <f>C5+D5</f>
+        <v>210887077</v>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>残高証明書との照合は未了（簿価評価）</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>売上総利益</t>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>売掛金</t>
         </is>
       </c>
       <c r="C6" s="7">
-        <f>PL!C15</f>
-        <v>219580189</v>
-      </c>
-      <c r="D6" s="7">
-        <f>PL!E15</f>
-        <v>211295514</v>
+        <f>'BS(借方)'!E7</f>
+        <v>19608899</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="E6" s="7">
-        <f>PL!G15</f>
-        <v>199010966</v>
-      </c>
-      <c r="F6" s="7">
-        <f>AVERAGE(C6:E6)</f>
-        <v>209962223</v>
-      </c>
-      <c r="G6" s="7">
-        <f>AVERAGE(D6:E6)</f>
-        <v>205153240</v>
-      </c>
-      <c r="H6" s="19" t="inlineStr"/>
+        <f>C6+D6</f>
+        <v>19608899</v>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>年齢表未受領のため簿価評価（長期滞留の有無は要確認）</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>売上総利益率</t>
-        </is>
-      </c>
-      <c r="C7" s="15">
-        <f>IFERROR(C6/C5,"")</f>
-        <v>0.186323479252075</v>
-      </c>
-      <c r="D7" s="15">
-        <f>IFERROR(D6/D5,"")</f>
-        <v>0.178768974597464</v>
-      </c>
-      <c r="E7" s="15">
-        <f>IFERROR(E6/E5,"")</f>
-        <v>0.166411979362014</v>
-      </c>
-      <c r="H7" s="19" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>資材肥料売掛金</t>
+        </is>
+      </c>
+      <c r="C7" s="7">
+        <f>'BS(借方)'!E8</f>
+        <v>1227419</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="7">
+        <f>C7+D7</f>
+        <v>1227419</v>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>販売費及び一般管理費</t>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>棚卸資産</t>
         </is>
       </c>
       <c r="C8" s="7">
-        <f>PL!C16</f>
-        <v>214823441</v>
-      </c>
-      <c r="D8" s="7">
-        <f>PL!E16</f>
-        <v>215718454</v>
+        <f>'BS(借方)'!E9</f>
+        <v>14596695</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="E8" s="7">
-        <f>PL!G16</f>
-        <v>193151054</v>
-      </c>
-      <c r="F8" s="7">
-        <f>AVERAGE(C8:E8)</f>
-        <v>207897649.666667</v>
-      </c>
-      <c r="G8" s="7">
-        <f>AVERAGE(D8:E8)</f>
-        <v>204434754</v>
-      </c>
-      <c r="H8" s="19" t="inlineStr"/>
+        <f>C8+D8</f>
+        <v>14596695</v>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>青果物は短期回転。資材（パック・容器）の滞留有無は要確認（簿価評価）</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>営業利益</t>
-        </is>
-      </c>
-      <c r="C9" s="18">
-        <f>PL!C17</f>
-        <v>4756748</v>
-      </c>
-      <c r="D9" s="18">
-        <f>PL!E17</f>
-        <v>-4422940</v>
-      </c>
-      <c r="E9" s="18">
-        <f>PL!G17</f>
-        <v>5859912</v>
-      </c>
-      <c r="F9" s="18">
-        <f>AVERAGE(C9:E9)</f>
-        <v>2064573.33333333</v>
-      </c>
-      <c r="G9" s="18">
-        <f>AVERAGE(D9:E9)</f>
-        <v>718486</v>
-      </c>
-      <c r="H9" s="19" t="inlineStr"/>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>立替金</t>
+        </is>
+      </c>
+      <c r="C9" s="7">
+        <f>'BS(借方)'!E10</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="7">
+        <f>C9+D9</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>簿価評価</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>減価償却費</t>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>未収入金</t>
         </is>
       </c>
       <c r="C10" s="7">
-        <f>SGA!C31</f>
-        <v>13663684</v>
-      </c>
-      <c r="D10" s="7">
-        <f>SGA!E31</f>
-        <v>12557564</v>
+        <f>'BS(借方)'!E11</f>
+        <v>3011112</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="E10" s="7">
-        <f>SGA!G31</f>
-        <v>8878970</v>
-      </c>
-      <c r="F10" s="7">
-        <f>AVERAGE(C10:E10)</f>
-        <v>11700072.6666667</v>
-      </c>
-      <c r="G10" s="7">
-        <f>AVERAGE(D10:E10)</f>
-        <v>10718267</v>
-      </c>
-      <c r="H10" s="19" t="inlineStr"/>
+        <f>C10+D10</f>
+        <v>3011112</v>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>センター費・完納奨励金等。簿価評価</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>EBITDA（営業利益＋減価償却費）</t>
-        </is>
-      </c>
-      <c r="C11" s="9">
-        <f>C9+C10</f>
-        <v>18420432</v>
-      </c>
-      <c r="D11" s="9">
-        <f>D9+D10</f>
-        <v>8134624</v>
-      </c>
-      <c r="E11" s="9">
-        <f>E9+E10</f>
-        <v>14738882</v>
-      </c>
-      <c r="F11" s="9">
-        <f>AVERAGE(C11:E11)</f>
-        <v>13764646</v>
-      </c>
-      <c r="G11" s="9">
-        <f>AVERAGE(D11:E11)</f>
-        <v>11436753</v>
-      </c>
-      <c r="H11" s="19" t="inlineStr"/>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>前払費用</t>
+        </is>
+      </c>
+      <c r="C11" s="7">
+        <f>'BS(借方)'!E12</f>
+        <v>83575</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7">
+        <f>C11+D11</f>
+        <v>83575</v>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>簿価評価</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>【調整項目】</t>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>仮払金</t>
+        </is>
+      </c>
+      <c r="C12" s="7">
+        <f>'BS(借方)'!E13</f>
+        <v>493135</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7">
+        <f>C12+D12</f>
+        <v>493135</v>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>簿価評価</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>代表者及びその家族分の役員報酬（実績）</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>10680000</v>
+          <t>仮払税金等</t>
+        </is>
+      </c>
+      <c r="C13" s="7">
+        <f>'BS(借方)'!E14</f>
+        <v>0</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>10680000</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>4440000</v>
-      </c>
-      <c r="H13" s="19" t="inlineStr">
-        <is>
-          <t>勘定科目内訳書「人件費の内訳」</t>
+        <v>0</v>
+      </c>
+      <c r="E13" s="7">
+        <f>C13+D13</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>簿価評価</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>後任経営者の想定報酬（仮定）</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="H14" s="19" t="inlineStr">
-        <is>
-          <t>（仮定）年8,000千円。譲渡後の経営体制により見直す</t>
+          <t>貸倒引当金</t>
+        </is>
+      </c>
+      <c r="C14" s="7">
+        <f>'BS(借方)'!E15</f>
+        <v>-203000</v>
+      </c>
+      <c r="D14" s="7">
+        <f>-C14</f>
+        <v>203000</v>
+      </c>
+      <c r="E14" s="7">
+        <f>C14+D14</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>個別に回収可能性を判断するため全額戻入（貸倒実績は要確認）</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>①役員報酬の正常化</t>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>建物</t>
         </is>
       </c>
       <c r="C15" s="7">
-        <f>C13-C14</f>
-        <v>2680000</v>
-      </c>
-      <c r="D15" s="7">
-        <f>D13-D14</f>
-        <v>2680000</v>
+        <f>'BS(借方)'!E18</f>
+        <v>92065694</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="E15" s="7">
-        <f>E13-E14</f>
-        <v>-3560000</v>
-      </c>
-      <c r="F15" s="7">
-        <f>AVERAGE(C15:E15)</f>
-        <v>600000</v>
-      </c>
-      <c r="G15" s="7">
-        <f>AVERAGE(D15:E15)</f>
-        <v>-440000</v>
-      </c>
-      <c r="H15" s="19" t="inlineStr">
-        <is>
-          <t>代表者・配偶者報酬を後任経営者想定報酬に置換（仮定）。常務取締役（2026/5退任、年6,600千円）の後任要否は要確認のため調整対象外</t>
+        <f>C15+D15</f>
+        <v>92065694</v>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>固定資産台帳未受領のため簿価評価（定額法で償却不足なし：別表十六）。固定資産税評価額は47,062千円</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>②賞与の正常化</t>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>建物付属設備</t>
         </is>
       </c>
       <c r="C16" s="7">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="7">
-        <f>0</f>
+        <f>'BS(借方)'!E19</f>
+        <v>11399836</v>
+      </c>
+      <c r="D16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="7">
-        <f>-AVERAGE(SGA!C7,SGA!E7)</f>
-        <v>-5847325</v>
-      </c>
-      <c r="F16" s="7">
-        <f>AVERAGE(C16:E16)</f>
-        <v>-1949108.33333333</v>
-      </c>
-      <c r="G16" s="7">
-        <f>AVERAGE(D16:E16)</f>
-        <v>-2923662.5</v>
-      </c>
-      <c r="H16" s="19" t="inlineStr">
-        <is>
-          <t>2026/3期は賞与計上なし。前2期平均相当を費用として控除（仮説：今後支給が再開される前提）。不支給の経緯は要確認</t>
+        <f>C16+D16</f>
+        <v>11399836</v>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>簿価評価</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>③受取奨励金（純額）の加算</t>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>構築物</t>
         </is>
       </c>
       <c r="C17" s="7">
-        <f>PL!C20-PL!C26</f>
-        <v>2178508</v>
-      </c>
-      <c r="D17" s="7">
-        <f>PL!E20-PL!E26</f>
-        <v>2314707</v>
+        <f>'BS(借方)'!E20</f>
+        <v>284395</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="E17" s="7">
-        <f>PL!G20-PL!G26</f>
-        <v>2418448</v>
-      </c>
-      <c r="F17" s="7">
-        <f>AVERAGE(C17:E17)</f>
-        <v>2303887.66666667</v>
-      </c>
-      <c r="G17" s="7">
-        <f>AVERAGE(D17:E17)</f>
-        <v>2366577.5</v>
-      </c>
-      <c r="H17" s="19" t="inlineStr">
-        <is>
-          <t>仕入完納等に伴い毎期経常的に発生する事業関連収益（受取奨励金−出荷奨励金）。発生根拠は要確認</t>
+        <f>C17+D17</f>
+        <v>284395</v>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>簿価評価</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>調整額 計</t>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>機械装置</t>
         </is>
       </c>
       <c r="C18" s="7">
-        <f>C15+C16+C17</f>
-        <v>4858508</v>
-      </c>
-      <c r="D18" s="7">
-        <f>D15+D16+D17</f>
-        <v>4994707</v>
+        <f>'BS(借方)'!E21</f>
+        <v>2</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="E18" s="7">
-        <f>E15+E16+E17</f>
-        <v>-6988877</v>
-      </c>
-      <c r="F18" s="7">
-        <f>AVERAGE(C18:E18)</f>
-        <v>954779.333333333</v>
-      </c>
-      <c r="G18" s="7">
-        <f>AVERAGE(D18:E18)</f>
-        <v>-997085</v>
-      </c>
-      <c r="H18" s="19" t="inlineStr"/>
+        <f>C18+D18</f>
+        <v>2</v>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>簿価評価</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>調整後EBITDA</t>
-        </is>
-      </c>
-      <c r="C19" s="11">
-        <f>C11+C18</f>
-        <v>23278940</v>
-      </c>
-      <c r="D19" s="11">
-        <f>D11+D18</f>
-        <v>13129331</v>
-      </c>
-      <c r="E19" s="11">
-        <f>E11+E18</f>
-        <v>7750005</v>
-      </c>
-      <c r="F19" s="11">
-        <f>AVERAGE(C19:E19)</f>
-        <v>14719425.3333333</v>
-      </c>
-      <c r="G19" s="11">
-        <f>AVERAGE(D19:E19)</f>
-        <v>10439668</v>
-      </c>
-      <c r="H19" s="19" t="inlineStr"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>車両運搬具</t>
+        </is>
+      </c>
+      <c r="C19" s="7">
+        <f>'BS(借方)'!E22</f>
+        <v>15</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="7">
+        <f>C19+D19</f>
+        <v>15</v>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>簿価評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>工具器具備品</t>
+        </is>
+      </c>
+      <c r="C20" s="7">
+        <f>'BS(借方)'!E23</f>
+        <v>18546</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7">
+        <f>C20+D20</f>
+        <v>18546</v>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>簿価評価</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>経常利益</t>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>土地</t>
         </is>
       </c>
       <c r="C21" s="7">
-        <f>PL!C29</f>
-        <v>11316540</v>
+        <f>'BS(借方)'!E24</f>
+        <v>93137240</v>
       </c>
       <c r="D21" s="7">
-        <f>PL!E29</f>
-        <v>2181381</v>
+        <f>47477508/0.7-C21</f>
+        <v>-25312228.5714286</v>
       </c>
       <c r="E21" s="7">
-        <f>PL!G29</f>
-        <v>8067784</v>
-      </c>
-      <c r="F21" s="7">
-        <f>AVERAGE(C21:E21)</f>
-        <v>7188568.33333333</v>
-      </c>
-      <c r="G21" s="7">
-        <f>AVERAGE(D21:E21)</f>
-        <v>5124582.5</v>
-      </c>
-      <c r="H21" s="19" t="inlineStr"/>
+        <f>C21+D21</f>
+        <v>67825011.4285714</v>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>固定資産税評価額（R8年度）47,478千円÷0.7で時価を推計（鑑定・路線価で要確認）</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>当期純利益</t>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>電話加入権</t>
         </is>
       </c>
       <c r="C22" s="7">
-        <f>PL!C39</f>
-        <v>9106898</v>
+        <f>'BS(借方)'!E28</f>
+        <v>2155595</v>
       </c>
       <c r="D22" s="7">
-        <f>PL!E39</f>
-        <v>2928899</v>
+        <f>-C22</f>
+        <v>-2155595</v>
       </c>
       <c r="E22" s="7">
-        <f>PL!G39</f>
-        <v>-15084655</v>
-      </c>
-      <c r="F22" s="7">
-        <f>AVERAGE(C22:E22)</f>
-        <v>-1016286</v>
-      </c>
-      <c r="G22" s="7">
-        <f>AVERAGE(D22:E22)</f>
-        <v>-6077878</v>
-      </c>
-      <c r="H22" s="19" t="inlineStr"/>
+        <f>C22+D22</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>換金価値なしとしてゼロ評価</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>支払利息</t>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>ソフトウェア</t>
         </is>
       </c>
       <c r="C23" s="7">
-        <f>PL!C25</f>
-        <v>3962441</v>
-      </c>
-      <c r="D23" s="7">
-        <f>PL!E25</f>
-        <v>4040547</v>
+        <f>'BS(借方)'!E29</f>
+        <v>371800</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="E23" s="7">
-        <f>PL!G25</f>
-        <v>3895556</v>
-      </c>
-      <c r="F23" s="7">
-        <f>AVERAGE(C23:E23)</f>
-        <v>3966181.33333333</v>
-      </c>
-      <c r="G23" s="7">
-        <f>AVERAGE(D23:E23)</f>
-        <v>3968051.5</v>
-      </c>
-      <c r="H23" s="19" t="inlineStr"/>
+        <f>C23+D23</f>
+        <v>371800</v>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>簿価評価</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>人件費（役員報酬・給与・賞与・法定福利等）</t>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>投資有価証券</t>
         </is>
       </c>
       <c r="C24" s="7">
-        <f>SGA!C5+SGA!C6+SGA!C7+SGA!C8+SGA!C9+SGA!C10+SGA!C11</f>
-        <v>120274546</v>
-      </c>
-      <c r="D24" s="7">
-        <f>SGA!E5+SGA!E6+SGA!E7+SGA!E8+SGA!E9+SGA!E10+SGA!E11</f>
-        <v>121407097</v>
+        <f>'BS(借方)'!E32</f>
+        <v>2600000</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>7242000</v>
       </c>
       <c r="E24" s="7">
-        <f>SGA!G5+SGA!G6+SGA!G7+SGA!G8+SGA!G9+SGA!G10+SGA!G11</f>
-        <v>104562438</v>
-      </c>
-      <c r="F24" s="7">
-        <f>AVERAGE(C24:E24)</f>
-        <v>115414693.666667</v>
-      </c>
-      <c r="G24" s="7">
-        <f>AVERAGE(D24:E24)</f>
-        <v>112984767.5</v>
-      </c>
-      <c r="H24" s="19" t="inlineStr"/>
+        <f>C24+D24</f>
+        <v>9842000</v>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>フィデアHD株式3,000株を2026/9/18終値2,814円で時価評価（算定日終値で要更新）。(株)庄果株式・鶴岡信金出資は簿価</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>運賃＋車両関連費</t>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>出資金</t>
         </is>
       </c>
       <c r="C25" s="7">
-        <f>SGA!C16+SGA!C15</f>
-        <v>36022052</v>
-      </c>
-      <c r="D25" s="7">
-        <f>SGA!E16+SGA!E15</f>
-        <v>39619785</v>
+        <f>'BS(借方)'!E33</f>
+        <v>75000</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="E25" s="7">
-        <f>SGA!G16+SGA!G15</f>
-        <v>38858196</v>
-      </c>
-      <c r="F25" s="7">
-        <f>AVERAGE(C25:E25)</f>
-        <v>38166677.6666667</v>
-      </c>
-      <c r="G25" s="7">
-        <f>AVERAGE(D25:E25)</f>
-        <v>39238990.5</v>
-      </c>
-      <c r="H25" s="19" t="inlineStr"/>
+        <f>C25+D25</f>
+        <v>75000</v>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>簿価評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>長期前払費用</t>
+        </is>
+      </c>
+      <c r="C26" s="7">
+        <f>'BS(借方)'!E34</f>
+        <v>74500</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="7">
+        <f>C26+D26</f>
+        <v>74500</v>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>簿価評価（僅少）</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>【進行期：2026年4〜7月（4か月累計）】</t>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>保証金</t>
+        </is>
+      </c>
+      <c r="C27" s="7">
+        <f>'BS(借方)'!E35</f>
+        <v>33302569</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="7">
+        <f>C27+D27</f>
+        <v>33302569</v>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>庄内青果物卸売精算(有)31,993千円ほか。返還条件未確認のため簿価評価（要確認）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>売上高</t>
+          <t>事業保険積立金</t>
         </is>
       </c>
       <c r="C28" s="7">
-        <f>PL!I10</f>
-        <v>411154947</v>
+        <f>'BS(借方)'!E36</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="7">
+        <f>C28+D28</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>2026/3期に全額取崩し済</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>売上総利益</t>
+          <t>繰延資産</t>
         </is>
       </c>
       <c r="C29" s="7">
-        <f>PL!I15</f>
-        <v>61213573</v>
-      </c>
+        <f>'BS(借方)'!E39</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="7">
+        <f>C29+D29</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="18" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>営業利益</t>
-        </is>
-      </c>
-      <c r="C30" s="7">
-        <f>PL!I17</f>
-        <v>5316980</v>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>資産合計</t>
+        </is>
+      </c>
+      <c r="C30" s="9">
+        <f>SUM(C5:C29)</f>
+        <v>485190104</v>
+      </c>
+      <c r="D30" s="9">
+        <f>SUM(D5:D29)</f>
+        <v>-20022823.5714286</v>
+      </c>
+      <c r="E30" s="9">
+        <f>SUM(E5:E29)</f>
+        <v>465167280.428571</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>減価償却費</t>
+          <t>買掛金</t>
         </is>
       </c>
       <c r="C31" s="7">
-        <f>SGA!I31</f>
-        <v>2436000</v>
+        <f>'BS (貸方)'!E6</f>
+        <v>26349122</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="7">
+        <f>C31+D31</f>
+        <v>26349122</v>
+      </c>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>簿価評価</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>経常利益</t>
+          <t>未払金</t>
         </is>
       </c>
       <c r="C32" s="7">
-        <f>PL!I29</f>
-        <v>5884887</v>
+        <f>'BS (貸方)'!E7</f>
+        <v>6630301</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="7">
+        <f>C32+D32</f>
+        <v>6630301</v>
+      </c>
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>3/16〜3/31の未払給与2,837千円は計上済のため追加計上なし</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>売上総利益率</t>
-        </is>
-      </c>
-      <c r="C33" s="15">
-        <f>IFERROR(C29/C28,"")</f>
-        <v>0.148882005303952</v>
+          <t>仮受金</t>
+        </is>
+      </c>
+      <c r="C33" s="7">
+        <f>'BS (貸方)'!E8</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="7">
+        <f>C33+D33</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>簿価評価</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>前期同期間（4〜7月）売上高：概況説明書月別</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>419288000</v>
-      </c>
-      <c r="H34" s="19" t="inlineStr">
-        <is>
-          <t>2025年4〜7月の月別売上合計（千円単位の記載を円換算）</t>
+          <t>預り金</t>
+        </is>
+      </c>
+      <c r="C34" s="7">
+        <f>'BS (貸方)'!E9</f>
+        <v>281300</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="7">
+        <f>C34+D34</f>
+        <v>281300</v>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>簿価評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>未払法人税等</t>
+        </is>
+      </c>
+      <c r="C35" s="7">
+        <f>'BS (貸方)'!E10</f>
+        <v>1851300</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="7">
+        <f>C35+D35</f>
+        <v>1851300</v>
+      </c>
+      <c r="F35" s="18" t="inlineStr">
+        <is>
+          <t>簿価評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>未払消費税</t>
+        </is>
+      </c>
+      <c r="C36" s="7">
+        <f>'BS (貸方)'!E11</f>
+        <v>2167500</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="7">
+        <f>C36+D36</f>
+        <v>2167500</v>
+      </c>
+      <c r="F36" s="18" t="inlineStr">
+        <is>
+          <t>簿価評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>長期借入金</t>
+        </is>
+      </c>
+      <c r="C37" s="7">
+        <f>'BS (貸方)'!E14</f>
+        <v>361058000</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="7">
+        <f>C37+D37</f>
+        <v>361058000</v>
+      </c>
+      <c r="F37" s="18" t="inlineStr">
+        <is>
+          <t>1年内返済額の区分なし。額面で評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>預り保証金</t>
+        </is>
+      </c>
+      <c r="C38" s="7">
+        <f>'BS (貸方)'!E15</f>
+        <v>8980000</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="7">
+        <f>C38+D38</f>
+        <v>8980000</v>
+      </c>
+      <c r="F38" s="18" t="inlineStr">
+        <is>
+          <t>仲卸業者・買参人等からの預りと推察。返還義務ありとして額面評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>賞与引当金</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="7">
+        <f>C39+D39</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="18" t="inlineStr">
+        <is>
+          <t>2026/3期は賞与支給なし・規程未受領のため計上せず（要確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>退職給付引当金</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="7">
+        <f>C40+D40</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="18" t="inlineStr">
+        <is>
+          <t>中小企業退職金共済に加入（掛金3,026千円/年）。外部積立で充足と推定し計上せず（退職金規程で要確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>繰延税金負債（税効果）</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="7">
+        <f>(D14+D24)*0.34</f>
+        <v>2531300</v>
+      </c>
+      <c r="E41" s="7">
+        <f>C41+D41</f>
+        <v>2531300</v>
+      </c>
+      <c r="F41" s="18" t="inlineStr">
+        <is>
+          <t>貸倒引当金戻入・有価証券評価益に実効税率34%で税効果を認識。土地評価損・電話加入権は売却予定がなく実現可能性が低いため認識しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>負債合計</t>
+        </is>
+      </c>
+      <c r="C42" s="9">
+        <f>SUM(C31:C41)</f>
+        <v>407317523</v>
+      </c>
+      <c r="D42" s="9">
+        <f>SUM(D31:D41)</f>
+        <v>2531300</v>
+      </c>
+      <c r="E42" s="9">
+        <f>SUM(E31:E41)</f>
+        <v>409848823</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>純資産（時価純資産）</t>
+        </is>
+      </c>
+      <c r="C43" s="11">
+        <f>C30-C42</f>
+        <v>77872581</v>
+      </c>
+      <c r="D43" s="11">
+        <f>D30-D42</f>
+        <v>-22554123.5714286</v>
+      </c>
+      <c r="E43" s="11">
+        <f>E30-E42</f>
+        <v>55318457.4285715</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>チェック：帳簿純資産と一致</t>
+        </is>
+      </c>
+      <c r="C44" t="b">
+        <f>EXACT(C43,'BS (貸方)'!E22)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>※評価できなかった科目（売掛金・棚卸資産・建物・保証金・退職給付等）は簿価評価とし、上記事由に記載。DDで追加調整の余地がある。</t>
         </is>
       </c>
     </row>
